--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -521,41 +521,10 @@
       </c>
     </row>
     <row r="2" ht="39.95" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>วางรายละเอียดสินค้าจาก Shopee ทั้งหมดที่นี่</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>https://s.lazada.co.th/xxx</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://down-th.img.susercontent.com/xxx.jpg</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ลด 20%</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="345" customHeight="1">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>RAY-BAN JUSTIN- RB4165F 601/71
 Ray-Ban เรแบนเป็นผู้นำด้านการผลิตแว่นกันแดด และแว่นสายตา ที่ได้ความนิยมมากที่สุดทั่วโลก มีให้เลือกหลากหลายสไตล์ เหมาะกับทุกคน และใส่ได้ทั้งผู้หญิงและผู้ชาย
@@ -569,23 +538,23 @@
 Lens Material: Polycarbonate Standard</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/AUqz80oxUd</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6PzJE?c=b&amp;t=p-ijr1Q-svKWG</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134201-7r990-lscec08f21gm73.webp
 https://down-th.img.susercontent.com/file/th-11134201-7r98y-lscec0amysmu78.webp</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿5,130
 final price indicator icon
@@ -597,17 +566,17 @@
 </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>done 2026-05-21 13:15</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="409.5" customHeight="1">
-      <c r="A4" t="n">
+    <row r="3" ht="345" customHeight="1">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Sony BRAVIA 3 ทีวี 55 นิ้ว รุ่น K-55S30 4K Ultra HD Smart TV (Google TV) | 4K HDR Processor X1
 รายละเอียดสินค้า
@@ -627,22 +596,22 @@
 เรียกดูภาพยนตร์และรายการทีวีมากกว่า 400,000 ตอนจากบริการสตรีมมิ่งของคุณทั้งหมดในที่เดียว โดยจัดเป็นหัวข้อและแนวเนื้อหาไว้ตามสิ่งที่คุณสนใจ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>https://s.shopee.co.th/10zvLKc6Ji</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7r98v-lvsn9yh5vql9c5.webp</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">฿20,500
 final price indicator icon
@@ -650,6 +619,136 @@
 โค้ดส่วนลดร้านค้า
 ลด ฿1.99k
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409.5" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>เบาะพกพา เบาะสุขภาพ เบาะเก้าอี้ เบาะรองเอว นั่งนานไม่เมื่อย เบาะรองนั่งเพื่อสุขภาพ เก้าอี้รองปรับท่านั่ง หมอนรองหลัง</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVQzcZ3Ip</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-7qul7-lgesv2vzlg0ec1.webp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ลด 69% เหลือ ฿499 (ปกติ ฿1,599)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>(พร้อมส่งจากไทย) เบาะรองนั่ง พร้อมพิงหลัง หูการ์ตุน มีสายรัดเก้าอี้ เบาะรองหลัง</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1Zl7G3F4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-7r98z-ln4pqmcm29mxa6.webp</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ลด 5% เริ่มต้น ฿160 - ฿199</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ไฟฟ้า High-End เก้าอี้สํานักงานหนังแท้ Boss เก้าอี้ขนาดใหญ่ Ergonomic เก้าอี้ Reclining Liftable นวดบ้านการเรียนรู้เก้าอี้คอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8piujnmmou</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/sg-11134201-824j0-mdzysm91y1a830.webp</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ลด 50% เริ่มต้น ฿14,534 - ฿43,359</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[ลดอาการปวดข้อมือ] แผ่นรองเมาส์/ที่รองข้อมือ/เมมโมรี่โฟม/แผ่นรองคีย์บอร์ด</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HGYal3GC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/sg-11134201-825zp-mkjcbxcbzz7s79.webp</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ลด 49% เริ่มต้น ฿163 - ฿183</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Screenbar Light Bar โคมไฟแขวนจอคอม LED ปรับไฟได้ 3 สี ปรับองศาได้หลายมุม ลดแสงสีฟ้า</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VKzxnaa2h</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://down-th.img.susercontent.com/file/th-11134207-7r98p-lvcxws3wijsqf6.webp</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ลด 46% เริ่มต้น ฿269 - ฿700</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -621,6 +621,11 @@
 </t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>done 2026-05-27 11:12</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="409.5" customHeight="1">
       <c r="A4" t="n">
@@ -636,7 +641,11 @@
           <t>https://s.shopee.co.th/2LVQzcZ3Ip</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://s.lazada.co.th/s.Z6mEyG?c=a&amp;t=p-i0-s0&amp;sub_id1=W1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7qul7-lgesv2vzlg0ec1.webp</t>
@@ -662,7 +671,6 @@
           <t>https://s.shopee.co.th/6L1Zl7G3F4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7r98z-ln4pqmcm29mxa6.webp</t>
@@ -688,7 +696,6 @@
           <t>https://s.shopee.co.th/8piujnmmou</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/sg-11134201-824j0-mdzysm91y1a830.webp</t>
@@ -714,7 +721,6 @@
           <t>https://s.shopee.co.th/70HGYal3GC</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/sg-11134201-825zp-mkjcbxcbzz7s79.webp</t>
@@ -740,7 +746,6 @@
           <t>https://s.shopee.co.th/6VKzxnaa2h</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>https://down-th.img.susercontent.com/file/th-11134207-7r98p-lvcxws3wijsqf6.webp</t>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -656,6 +656,11 @@
           <t>ลด 69% เหลือ ฿499 (ปกติ ฿1,599)</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>done 2026-05-27 12:06</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -686,6 +686,11 @@
           <t>ลด 5% เริ่มต้น ฿160 - ฿199</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>done 2026-06-01 12:52</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -716,6 +716,11 @@
           <t>ลด 50% เริ่มต้น ฿14,534 - ฿43,359</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 11:59</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -746,6 +746,11 @@
           <t>ลด 49% เริ่มต้น ฿163 - ฿183</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>done 2026-06-05 22:48</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -776,6 +776,11 @@
           <t>ลด 46% เริ่มต้น ฿269 - ฿700</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>done 2026-06-08 12:16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -782,6 +782,133 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LENODI ตู้เย็นมินิ 5.2Q สองประตู ประหยัดพลังงาน ตู้เย็นในบ้านขนาดเล็ก ตู้เย็น 2 ประตู รุ่นEPLD-128A จุได้ถึง 148 ลิตร ราคา 1649.00 บาท</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V6PSGXZ3C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mfngpcxzyy2we9.webp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TCL ตู้เย็น Side by Side ขนาด 17.5Q/505L ระบบ Inverter ละลายน้ำแข็งอัตโนมัติ รุ่น P505SBN/RT50MPSBG ราคา 15490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AayMA6qAc</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mozm4emq56312d.webp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kingc'ool ตู้แช่เครื่องดื่ม 3 ประตู 56คิว จัมโบ้ ตู้แช่มินิมาร์ท รุ่นประหยัดไฟพิเศษ คุณภาพดี ถึกทน ราคา 39900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbn2wdXRL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mmip7ct3e51d0c.webp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>เครื่องดูดฝุ่น 35L ดูดแห้ง/ดูดน้ำ/เป่าลม พลังสูง 2200W vacuum cleaner ต้องมีสำหรับร้านรถยนต์ ราคา 1419.00 บาท</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiUfvpZ4k</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-meb6m6gaswzo6d.webp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX บด ชง ตีฟองในเครื่องเดียว ราคา 18462.00 บาท</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNUcC2qDR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>done 2026-06-09 06:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -896,16 +896,141 @@
           <t>https://s.shopee.co.th/gNUcC2qDR</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>done 2026-06-09 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TV Direct - SANSHIRO พัดลมอุตสาหกรรม 20" FS-20 5 ใบพัด ราคา 1760.00 บาท</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qD3ZrL96T</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-ma3vs5aezunic4.webp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>83</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HAIER เครื่องปรับอากาศ รุ่น HSU-CQRC ขนาด 9200-24200 BTU ระบบ Fixed Speed Air Conditioner แอร์ ราคา 11240.00 บาท</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Ab1rwrct2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-ml4cxz9wdmo1e5.webp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>78</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Candy ตู้เย็นสองประตู ขนาด 8.3 คิว ความจุ 235 ลิตร ระบบอินเวอร์เตอร์ Inverter ประหยัดไฟ เบอร์ 5 ละลายน้ำแข็งอัตโนมัติ ราคา 7299.00 บาท</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZVW88HIL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mn4791eaybd0b9.webp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>102</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>kawu เครื่องนึ่งไฟฟ้าอเนกประสงค์ 3ชั้น หม้อนึ่งไฟฟ้า 24ลิตรความจุมาก หม้อนึ่งไฟฟ้า ไก่นึ่งได้ทั้งตัว ราคา 899.00 บาท</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20sviV4n31</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-miva3n0wouf766.webp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BONMECOM2 / ปลั๊กไฟ Melon/ ปลั๊กไฟโต๊ะคอม/ ปลั๊กไฟโต๊ะทำงาน 2 ช่อง 1 สวิตซ์ 3USB (1.5M) มี มอก. (ของแถมคละสี) ราคา 52.00 บาท</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AKY3da5f1i</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md9qzjt7ct6te4.webp</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 06:08</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1021,16 +1021,141 @@
           <t>https://s.shopee.co.th/AKY3da5f1i</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md9qzjt7ct6te4.webp</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>done 2026-06-10 06:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>59</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>⚡สินค้าพร้อมส่⚡Ksrain แอร์เคลื่อนที่ 30000BTU แอร์บ้านเล็ก portable air conditioner Touch Control LED Display มี 5โหมดกา ราคา 5190.00 บาท</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OWYO0O7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mmfsuclm7o5e13.webp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>39</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hisense เครื่องซักผ้าฝาหน้า Inverter รุ่น WF80N1E ความจุ 8 กก. สีขาว ราคา 8074.00 บาท</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gNY7tHgdV</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mp5is3bguhhq6d.webp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>93</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hisense ทีวี รุ่น 85E7Q ขนาด 85 นิ้ว QLED 4K Ultra HD Smart TV Vidaa OS Wi-Fi รุ่น E7Q ราคา 30240.00 บาท</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LOJIvQZob</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mp5iy5ioritce7.webp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[6.3-6.9|โค้ดลด 10%] ANKER eufy เครื่องดูดฝุ่นหุ่นยนต์ eufy Omni C20,7000 Pa ดูดทรงพลัง,ตัวบางเฉียบ 85 มม., การเปล่าด้วยตนเอง, ซักซับอัตโนมัติและอบแห้งอัตโนมัติสําหรับทําความสะอาดแบบแฮนด์ฟรี, สถานีออลอินวัน ราคา 9399.00 บาท</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4t6TiJx9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mojw0ztqfbwv8f.webp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Yotex หม้อทอดไร้น้ำมัน AirFryer 8 ลิตร ทอดเร็ว 1500W หม้ออบลมร้อน ดีไซน์แบบหมุนคู่ ดีไซน์มินิมอล หน้าต่างโปร่งใส ราคา 668.00 บาท</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47vlItbl</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp0hbammrpjha9.webp</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>done 2026-06-10 11:18</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1146,16 +1146,141 @@
           <t>https://s.shopee.co.th/W47vlItbl</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp0hbammrpjha9.webp</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>done 2026-06-10 11:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[New2026] Hisense ทีวี 4K ULED MiniLED Smart TV รุ่น EU6S ขนาด 55/65/75/85 นิ้ว 144Hz Game Mode Dolby Atmos ราคา 22090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATZ3h3r31</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mp371aww3iff81.webp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KENTO LITE 20000Pa เครื่องดูดฝุ่นไร้สาย สำหรับใช้ในบ้าน กำลังดูดแรง เครื่องดูดฝุ่นแบบไร้สายพกพา มาพร้อมไส้กรอง ราคา 404.00 บาท</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HbfUnRNJ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgyqwnqefmz20f.webp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>57</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[ประกัน3ปี] SKYWORTH 32 นิ้ว Google TV ทีวี HD Ready QLED+ Dolby Audio รุ่น 32Q60 รองรับ Netflix YouTube โหลดแอพได้ Wfi ราคา 5160.00 บาท</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXISnlQV9</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mozbik1h43k0de.webp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>De'Longhi เครื่องชงกาแฟเอสเพรสโซ่ Dedica Arte รุ่น EC885 สีเงิน สีเบจ และ สีเทา ราคา 12500.00 บาท</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGqUZEh1R</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qukw-lj44nlbrtdk83a.webp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Qpio 40L พัดลมไอเย็น แอร์เคลื่อนที่ พัดลมแอร์ พัดลมแอร์เย็นเคลื่อนที่ แอร์ตั้งพื้นพัดลมแอร์เย็นๆ เครื่องปรับอากาศเคลื่อ ราคา 769.00 บาท</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyBT9emG1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mf9cwj4meo7j8e.webp</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>done 2026-06-11 06:19</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -472,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1271,16 +1272,141 @@
           <t>https://s.shopee.co.th/6pyBT9emG1</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mf9cwj4meo7j8e.webp</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>done 2026-06-11 06:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>สั่งวันนี้ติดตั้งพรุ่งนี้💥แอร์ ไฮเออร์ Haier ระบบธรรมดา ติดตั้งฟรี ทั่วกรุงเทพ-ปริมณฑล ส่งฟรีทั่วไทย ราคา 12495.00 บาท</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXISwzSUZ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mog5bp76sp3d7b.webp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TCL WASH and DRY ซัก 12Kg. อบ 8Kg. เครื่องซักอบฝาหน้า รุ่น WT12EPWDW Inverter ประหยัดไฟ ทำงานเงียบ ราคา 13628.00 บาท</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50WXHpKLvr</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rc-moyuz7ani6fj3e.webp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>เตาปิ้งย่าง บาร์บีคิว กระทะปิ้งย่าง กระทะไฟฟ้า เตาปิ้งย่างอเนกประสงค์พร้อมหม้อสุกี้ ราคา 335.00 บาท</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9pbn2xnrJV</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mn5dwz9pd3i8a5.webp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MEIYIJIA เครื่องดูดฝุ่นในรถ ไร้สาย 12000Pa ​car vacuum cleaner เครื่องดูดฝุ่นขนาดเล็ก ที่ดูดฝุ่นในรถยนต์ ภายในบ้าน เตียง ราคา 268.00 บาท</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fIMqLzOpO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgyx989f9wjyee.webp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>โต๊ะรีดผ้าปรับได้ 10 ระดับ รองรับทุกท่ารีด 👍ร้านไทยส่งจากไทย🎉 หุ้มผ้าสะท้อนความร้อนแท้ 100% สีดำ ราคา 574.00 บาท</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiUgDiucz</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-megyhegt7lza86.webp</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 06:14</t>
         </is>
       </c>
     </row>
@@ -1295,4 +1421,25 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>{"last_personas": ["E", "B", "G", "E", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1397,16 +1397,141 @@
           <t>https://s.shopee.co.th/6AiUgDiucz</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-megyhegt7lza86.webp</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>done 2026-06-12 06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>100</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>🔌ปลั๊กไฟ 3/5 รู, หลายเต้ารับ, แถบสายไฟต่อ, ปลั๊กสายไฟต่อ, แจ็คชาร์จไฟ USB, รางปลั๊กไฟ, สายยาว 2/3/5M เมตร ราคา 78.00 บาท</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftgtOGhHU</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mifmrl2yr2mac9.webp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>109</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[Pre-Order till 07/07/26] Toshiba TV 85E450RP ทีวี 85 นิ้ว 4K Ultra HD Quantum Dot HDR10+ Dolby Atmos Smart TV ราคา 32490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70HbfhlHbY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mnmkbmxc3474fd.webp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>70</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Candy ตู้เย็นสองประตู ขนาด 8.3 คิว ความจุ 235 ลิตร ระบบอินเวอร์เตอร์ Inverter ประหยัดไฟ เบอร์ 5 ขจัดกลิ่นปะปน CRF-TMF235 ราคา 7649.00 บาท</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VhjVB0Trd</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-moywdhi3fvgh64.webp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ชุดนอนนา 3000W suoer พร้อมแผง 100 วัตต์ (ไม่รวมแบต) ชุดคอนโทรล ชาร์จเจอร์ โซล่าเซลล์ พลังงานแสงอาทิตย์ 12Vและ 12Vto 220V ราคา 4990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS2hn07BI</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/0ba76ea7cc49e06f779ea0ebcbb294ab.webp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>41</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[New 2026] Hisense TV 55/65/75/85 รุ่น EU7S สมาร์ททีวี 4K VIDAA Mini LED Pro 165Hz ULED TV ราคา 30090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDsGSVL3u</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp5iw9jzzh1d28.webp</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>done 2026-06-12 16:39</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1560,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1522,16 +1522,141 @@
           <t>https://s.shopee.co.th/7VDsGSVL3u</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp5iw9jzzh1d28.webp</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>done 2026-06-12 16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>53</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Toshiba TV 75C350RP ทีวี 75 นิ้ว 4K Ultra HD HDR10 Dolby Vision Atmos LED Wi-Fi Smart TV ราคา 23790.00 บาท</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4t6WPiU1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mhtudv3efkle0c.webp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Toshiba TV 55Z570SP ทีวี 55 นิ้ว 4K Quantum Dot Voice Control HDR10+ Dolby Vision Atmos Smart TV ราคา 15876.00 บาท</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGqUovEkV</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mogig3n8s7bj49.webp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[Best Seller] TCL แอร์ Full DC SaveIn AI Inverter ประหยัดไฟ ขนาด 9,200- 24,200 BTU รุ่น TAC-XALCH2 ราคา 8537.00 บาท</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZVVyXLyK</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mozm7fobwdn34f.webp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ตู้แช่เบียร์วุ้น KingCool รุ่น KX108-BF (108 ขวด) ขนาด 13 Q ( รับประกันนาน 10 ปี )มีพัดลมกระจายวุ้น ราคา 18900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1qZVWEEea3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-moqb27ta8palac.webp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>56</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>แบตเตอรี่12V 20Ah แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า ราคา 755.00 บาท</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/902g3FTHyJ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-82609-mkizr73xsbuw07.webp</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>done 2026-06-13 06:04</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1685,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1647,16 +1647,141 @@
           <t>https://s.shopee.co.th/902g3FTHyJ</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-82609-mkizr73xsbuw07.webp</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>done 2026-06-13 06:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ปลั๊กไฟพ่วงกลม 5 ช่อง 3 USB ความยาว 3 ,5, 8 เมตร ราคา 75.00 บาท</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/AAEdRXyoFE</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mopi2qw2tpfz5e.webp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Toshiba TV 55Z570 ทีวี 55 นิ้ว 4K Quantum Dot Voice Control HDR10+ Dolby Vision Atmos Smart TV ราคา 15876.00 บาท</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLHYvNbH5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp3eao4sruoc12.webp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>13</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NEW 2025 TCL TV รุ่น V6C ขนาด 75 นิ้ว 4K UHD Google TV รุ่น 75V6C HVA Panel ระบบปฏิบัติการ Google ราคา 22590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqiezs1G4</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mozmkh2aslxr5f.webp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>81</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[NEW 2025] TCL ทีวี 65 นิ้ว 4K UHD Google TV รุ่น 65V6C HVA Panel,Dynamic Color Enhancement,Dolby Audio &amp; HDR 10 ราคา 19824.00 บาท</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lSuHsmDw</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pr-moyuzcog2xvwcc.webp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>84</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>🛵แบตเตอรี่12V 20Ah 🛵แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า ราคา 940.00 บาท</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70Hbfe0ANc</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-825ad-mfw72a2atxceb0.webp</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>done 2026-06-14 05:47</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1810,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1772,16 +1772,141 @@
           <t>https://s.shopee.co.th/70Hbfe0ANc</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-825ad-mfw72a2atxceb0.webp</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>done 2026-06-14 05:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>64</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดวิดีโอพร้อมหน้าจอสําหรับบ้าน รุ่นกลางคืน วงแหวนประตูวิดีโอพูดสองทางระยะไกล 4.3 นิ้ว ไม่ต้อง ราคา 1304.00 บาท</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B4t6YFczr</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-7rblv-lov4s8p4xomr2e.webp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>124</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิทธิภาพพายุไซโคลนดูดแบบพกพาชาร์จเครื่องดูดฝุ่น ไร้สาย ที่ดูดฝุ่น ดูดฝุ่นในรถ ราคา 177.00 บาท</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4p7pKh</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m3w2qlqdirfr06.webp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[Flash Sale] AirdogX3Pro(D) เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ฆ่าเชื้อไวรัส ฟอร์มาลดีไฮด์พื้นที่30ตรม ราคา 19800.00 บาท</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W44PtO6Dz</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mojkshj50veq04.webp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[Flash Sale] AirdogX3Pro(D) เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ฆ่าเชื้อไวรัส ฟอร์มาลดีไฮด์พื้นที่30ตรม ราคา 19800.00 บาท</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g19hJra2E</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mojkshj50veq04.webp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>82</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TCL ตู้เย็น Free Builtin สี่ประตู สีขาว ขนาด 18.4Q / 521 ลิตร รุ่น RT52GCCDW ประหยัดไฟ ดีไซน์หรูหรา ราคา 29090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6L1usPlNee</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823oy-moyuz5h1sohu2b.webp</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:53</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1935,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1897,16 +1897,141 @@
           <t>https://s.shopee.co.th/6L1usPlNee</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823oy-moyuz5h1sohu2b.webp</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>done 2026-06-15 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>79</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TCL แอร์ Full DC Inverter ขนาด 24,200 BTU รุ่น TAC-XAL24CH2 เครื่องปรับอากาศ SaveIN AI Series เย็นเร็ว ทนทาน ประหยัดไฟ ราคา 18022.00 บาท</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OWbOia9</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823o9-moyuz5ghjnr65c.webp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>73</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NEW 2025 TCL TV รุ่น V6C ขนาด 43 นิ้ว 4K UHD Google TV รุ่น 43V6C HVA Panel ระบบปฏิบัติการ Google ราคา 9690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqif967Vo</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mozmipmiyg3w11.webp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>96</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>【ปรับปรุงใหม่และเพิ่มความหนาขึ้น】ปลั๊กสนาม 2x4 บล็อกยาง สาย VCT2x1 รองรับไฟสูงสุด 3000W ยาว 5M,10M,15M,20M,30M ราคา 79.00 บาท</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P4TpgY32</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-81zte-minvdih1cu0yc9.webp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>รุ่นใหม่ล่าสุด 2026 เครื่องทำน้ำแข็ง อัตโนมัติ ice maker ทำน้ำแข็งเร็ว ไม่ละลายใน 5 ชั่วโมง เครื่องทำน้ำแข็งขนาดเล็ก ราคา 2890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Vwf7LLpLV</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mnxxrt37bfuw22.webp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>61</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hisense ทีวี รุ่น 55E7Q 55″ QLED 4K Ultra HD Smart TV Vidaa OS Wi-Fi รุ่น 55E7Q ราคา 10706.00 บาท</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9KfWRsXOHE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp5izmcehfr5ff.webp</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>done 2026-06-15 05:57</t>
         </is>
       </c>
     </row>
@@ -1935,7 +2060,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2022,16 +2022,141 @@
           <t>https://s.shopee.co.th/9KfWRsXOHE</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp5izmcehfr5ff.webp</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>done 2026-06-15 05:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>75</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>พัดลม Hatari พัดลมอุตสาหกรรม 20 นิ้ว รับประกันมอเตอร์ 3 ปี (IP20M1) ราคา 2598.00 บาท</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftgtKZZHL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mkn9bny2kr2cdd.webp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>89</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Prisma LED TV Digital 24นิ้ว รุ่น DLE-2401DT ดิจิตอลทีวี รับประกันศูนย์ไทย 3ปี ราคา 2190.00 บาท</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATZ3ndiq0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lnw4rfs2h17re3.webp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>[NEW 2026] Roborock Saros 20 | เครื่องดูดฝุ่น ถูพื้น แรงดูดทรงพลัง 35,000 Pa. ซักม็อบด้วยอุณภูมิสูงสุด 100 องศา ราคา 39090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGqUa6ren</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp4vtb1egd1n6c.webp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NEW 2025 TCL ทีวี 75 นิ้ว 4K QLED Colorful Google TV รุ่น 75T6C HVA Panel ระบบปฏิบัติการ Google/Gaming TV/AIPQ/MEMC 60 H ราคา 25290.00 บาท</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BCLus6Jwz</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mozmk87rcow1a4.webp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>80</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>[New2026] Tineco Floor One Station S9 Artist - เครื่องล้างพื้นไร้สาย พร้อมแท่นเติมน้ำอัตโนมัติ 5ลิตร พลังฉีดน้ำแรงสูง ราคา 25799.00 บาท</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47vgTe8f</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-moyww4n752q411.webp</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>done 2026-06-16 06:26</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2185,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2147,16 +2147,141 @@
           <t>https://s.shopee.co.th/W47vgTe8f</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-moyww4n752q411.webp</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>done 2026-06-16 06:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>44</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ประกัน 5 ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้มือถือ เตารีดไอน้ำ เครื่องใช้ในครัวเรือน เตารีดไอน้ำ เตารีดไอน้ำแบบพกพา X ราคา 246.00 บาท</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5eHP3Wdx</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-ln2pq63i6vmbe6.webp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>111</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>HAIER แอร์ ขนาด 24,000 BTU ระบบ Inverter เครื่องปรับอากาศติดผนัง รุ่น HSU-24VQAC05 ผ่อน 0% ได้ ราคา 27328.00 บาท</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/40e06CBD0p</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-ml4cdi4d9ptz8a.webp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>19</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Toshiba TV 32E31RP ทีวี 32 นิ้ว HD Wifi รุ่น Dolby Audio Smart TV ราคา 4990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATVY0QGlp</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mp3edjfh1rt8bb.webp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio สี Midnight Black เครื่องดริปกาแฟ รวม การบด ชั่ง และชง ในเครื่องเดียว ราคา 26900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20sviGsVEO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>22</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>[ทักแชทก่อนสั่งซื้อ] โปรx6.6⚡️ส่วนลดคุ้มที่สุด 7เดือนแรก เครื่องกรองน้ำ COWAY 3 อุณหภูมิ ชำระรายเดือน ราคา 73.00 บาท</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6felGsaCig</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mowa2md7wv0ua6.webp</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:12</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2310,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2272,16 +2272,141 @@
           <t>https://s.shopee.co.th/6felGsaCig</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mowa2md7wv0ua6.webp</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>done 2026-06-17 06:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS VISION รุ่น GV9820E0 ราคา 21568.00 บาท</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g19hREX3k</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823ob-mozow83x883md0.webp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>13</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>รุ่นใหม่ล่าสุด 2026 เครื่องทำน้ำแข็ง อัตโนมัติ ice maker ทำน้ำแข็งเร็ว ไม่ละลายใน 5 ชั่วโมง เครื่องทำน้ำแข็งขนาดเล็ก ราคา 2890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W44Pu19Ad</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mnxxrt37bfuw22.webp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>112</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(รับประกันศูนย์ไทย 1 ปี) Xiaomi Smart Air Purifier 4 Lite/4 Compact/6/4Pro/Elite เครื่องฟอกอากาศ ราคา 2340.00 บาท</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPpem1tnT</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mnb2jj7egjcz5d.webp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>38</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>เครื่องอบลมร้อน ความจุ 12L ไฟ 1200W รุ่นMV-009 หม้อกระจายความร้อน พร้อมอุปกรณ์มาตรฐานในกล่อง รับประกัน 3 ปี ราคา 699.00 บาท</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkhjHADzm</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98w-lr32ynz35a3y01.webp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>51</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>HISENSE เครื่องซักผ้าฝาหน้า 10.5 กก. 1400 RPM อินเวอร์เตอร์ รุ่น WF105N1 สีเทา ราคา 11270.00 บาท</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7pqif5uGoz</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mp5is6cfx0jla9.webp</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>done 2026-06-17 06:16</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2435,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2397,16 +2397,141 @@
           <t>https://s.shopee.co.th/7pqif5uGoz</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mp5is6cfx0jla9.webp</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>done 2026-06-17 06:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>15</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Toshiba TV 75C350RP ทีวี 75 นิ้ว 4K Ultra HD HDR10 Dolby Vision Atmos LED Wi-Fi Smart TV ราคา 23790.00 บาท</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30lPOVAjzi</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp3egibrdtz433.webp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>done 2026-06-18 06:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>77</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Hisense TV รุ่น 65E6Q ทีวี 65 นิ้ว 4K Ultra HD Smart VIDAA TV Voice Control WIFI Netflix &amp; Youtube ราคา 14040.00 บาท</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXISqcAgb</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mp5iy7nk13i8c6.webp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>done 2026-06-18 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>54</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>🔥โปรx5🔥(🩵ส่วนลด 7เดือนแรก🩵) เครื่องกรองน้ำcoway รุ่น prime จ่าย 199.- ต่อเดือน (เปลี่ยนไส้กรองฟรี7ปี) ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3qKZtkVMKT</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mnr8p5khut5285.webp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>done 2026-06-18 06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>26</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>(พร้อมส่ง) ESUN เครื่องทำน้ำแข็ง Ice maker ความจุ 2.2 ลิตร รุ่น EIM-15 สินค้ารับประกัน 1 ปี ราคา 2450.00 บาท</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BCLucN609</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-ltoq718d19j3f1.webp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>done 2026-06-18 06:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Candy เครื่องซักอบผ้าฝาหน้า ซักอบ 11/7kg 2in1 ประหยัดไฟ สะอาด ฆ่าเชื้อและไรฝุ่น รับประกันมอเตอร์ 12 ปี CWDE110CPG2C2IU1 ราคา 10950.00 บาท</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLHYuGAQD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-moz9y245klq8b9.webp</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>done 2026-06-18 06:13</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2560,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2522,16 +2522,141 @@
           <t>https://s.shopee.co.th/6VLHYuGAQD</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-moz9y245klq8b9.webp</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>done 2026-06-18 06:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>103</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>แอร์ HAIER INVERTER รุ่น VRRA ลดกระหน่ำ 30-70% ส่งฟรีทั่วไทย WIFI อะไหล่ 5 ปี คอมเพลสเซอร์ 10 ปี ราคา 11899.00 บาท</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7fXISurKUX</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgbwb5pbl4aw51.webp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>99</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>HAIER แอร์ ขนาด 9,200 BTU ระบบ Inverter เครื่องปรับอากาศติดผนัง รุ่น HSU-09VQAC05 ผ่อน 0% ได้ ราคา 11871.00 บาท</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPpejt0ua</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-ml4c86c961vk2d.webp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>115</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูนย์ คอมเพลสเซอร์ 10ปี อะไหล่ 5ปี ติดตั้งพร้อมอุปกรณ์ ราคา 16890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9AM6FhQjmi</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mohglfzrd9fk45.webp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX บด ชง ตีฟองในเครื่องเดียว ราคา 18462.00 บาท</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS2hml3km</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lulivn98e2we52.webp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>16</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PETX FRESH BOX V.1 เครื่องกำจัดกลิ่นสัตว์เลี้ยง ดับกลิ่นฉี่แมว ฉี่สุนัข กรองขนสัตว์ ฟอกอากาศ PM2.5 ราคา 3990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8fPm8usC2H</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mkkusff6q8lh90.webp</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>done 2026-06-19 06:25</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2685,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "B", "G", "E", "B", "C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2647,16 +2647,141 @@
           <t>https://s.shopee.co.th/8fPm8usC2H</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mkkusff6q8lh90.webp</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>done 2026-06-19 06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>91</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>HAIER แอร์ ขนาด 12,300 BTU ระบบ Inverter เครื่องปรับอากาศติดผนัง รุ่น HSU-12VQAC05 ผ่อน 0% ได้ ราคา 13448.00 บาท</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkhjPOalX</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-ml4c9ybbneh059.webp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>65</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>[New 2026] Hisense TV 55 นิ้ว ULED MiniLED Smart TV 4K, 60 Hz รุ่น 55E8S ราคา 15590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2qS2hwQ2XF</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp5ixz57gu8c48.webp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>94</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ละเอียด บดปลาร้า บดปลา เครื่องบดเบอร์32 ราคา 3689.00 บาท</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1LdEvFhTGu</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul3-lj170s80fmqw10.webp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>18</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>แอร์เคลื่อนที่ All-in-one 1.5P/16000BTU แอร์ขนาดเล็ก Air mobile เย็นเร็ว เสียงเบา แอร์เคลื่อนที่ เย็น แอร์แบบเคลื่อนที่ ราคา 4989.00 บาท</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6py7xYLn1c</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mojjzh3j0g0fa4.webp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>49</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hisense ทีวี 40 นิ้ว Full HD VIDAA Smart TV รุ่น 40E4Q ราคา 5418.00 บาท</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6pyBTFcQH8</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp5iyos4nabv47.webp</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>done 2026-06-20 05:39</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2810,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "F", "A", "D", "F", "F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "มุกตลก", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม"], "last_roles": ["R3", "R7", "R1", "R6", "R8", "R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1"], "recent_captions": ["อันนี้เกินคาดจริงๆ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🔌ปลั๊กไฟ รู, หลายเต้ารับ, แถบสายไฟต่อ, ราคาแค่ 78 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Pre-Order till / Toshiba ราคาแค่ 32490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Candy ตู้เย็นสองประตู ขนาด . ราคาแค่ 7649 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ชุดนอนนา suoer พร้อมแผง วัตต์ ราคาแค่ 4990 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New Hisense TV / ราคาแค่ 30090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2772,16 +2772,141 @@
           <t>https://s.shopee.co.th/6pyBTFcQH8</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp5iyos4nabv47.webp</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>done 2026-06-20 05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>58</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกประสงค์ ชั้นนึ่ง3ชั้น รุ่น SC-532 กำลังไฟฟ้า 900 วัตต์ สินค้ารับประกัน 1 ปี ราคา 1090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6VLL4euPAs</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul9-lje3emrk0cr56a.webp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>67</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>[Presale พร้อมส่ง 12 มิย] Hisense เครื่องซักอบผ้าฝาหน้า Wash &amp; Dry Inverter รุ่น WD105N1E ความจุซัก 10.5 kg./ อบ 7 kg. ราคา 10390.00 บาท</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Ab1ruS2HS</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp5islshgxsd21.webp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>9</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio สี Midnight Black เครื่องดริปกาแฟ รวม การบด ชั่ง และชง ในเครื่องเดียว ราคา 26877.00 บาท</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AayM9459y</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mky2xiag4h6u10.webp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>50</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SMARTHOME เตาแม่เหล็กไฟฟ้า 1300W พร้อมหม้อและฝาแก้ว รุ่น IN-1300 ราคา 519.00 บาท</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVm6z2d0b</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m26exktsvcmc99.webp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>17</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>[ประกัน3ปี] SKYWORTH 55 นิ้ว Google TV 120Hz* ทีวี 4K QLED+ dbx-tv รุ่น 55Q60 รองรับNetflix YouTube โหลดแอพได้ Wifi ราคา 11490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9NgPcFMU</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mozc63skw2de1f.webp</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:51</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2935,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "C", "G", "C", "C", "E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การบอกต่อเฉยๆ", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "คำถาม", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R3", "R6", "R4", "R4", "R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ทีวีตัวนี้เลยครับ ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Best Seller TCL แอร์ ราคาแค่ 8537 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ตู้แช่เบียร์วุ้น KingCool รุ่น -BF ราคาแค่ 18900 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แบตเตอรี่ แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 755 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2897,16 +2897,141 @@
           <t>https://s.shopee.co.th/5L9NgPcFMU</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mozc63skw2de1f.webp</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>done 2026-06-21 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>12</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไวรัสรุ่นMTK-AP05(42 ตร.ม)HEPA13กรองฝุ่นและขนสัตว์เลี้ยง ราคา 6390.00 บาท</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4LGmywe1sM</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasd-matogng9t2d270.webp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>63</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>[New 2026] TCL BreezeIN แอร์ Inverter 23,900 BTU รุ่น TAC-BR24CSV/TD T-AI Energy Saving ประหยัดไฟเบอร์ 5 ควบคุมผ่าน App ราคา 24524.00 บาท</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkhjLMHzy</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp663x402brib2.webp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>[Online Exclusive] ตู้เย็นหน้ากระจก มินิบาร์ 50-90 ลิตร 1.8-3.2 คิว รุ่น RS-A50NG RS-A90NG ราคา 4690.00 บาท</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/60P4TuTFor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m1te385c2texde.webp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>34</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>[สินค้าใหม่] SMARTHOME หม้อทอดไร้น้ำมันขนาด 5.5 ลิตร รุ่น MV-1406 ราคา 1118.00 บาท</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50WXHqJGHG</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7qul3-lfezdjja4dkecf.webp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>88</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Smarthome เครื่องกรองอากาศ กรองและบอกระดับ PM2.5 รุ่น AP-180 ราคา 1776.00 บาท</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATZ3nVohB</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/0dadcbb3ecef12f74818a56da19dc6ea.webp</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>done 2026-06-21 05:56</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3060,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["E", "C", "A", "C", "H", "B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R5", "R6", "R5", "R7", "R2", "R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ปลั๊กไฟพ่วงกลม ช่อง USB ความยาว ราคาแค่ 75 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 15876 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL TV รุ่น ราคาแค่ 22590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 19824 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 🛵แบตเตอรี่ 🛵แบตเตอรี่แห้งแท้ รุ่น -DZF- ราคาแค่ 940 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3022,16 +3022,141 @@
           <t>https://s.shopee.co.th/8ATZ3nVohB</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/0dadcbb3ecef12f74818a56da19dc6ea.webp</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>done 2026-06-21 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>90</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>TCL ตู้เย็น Side by Side ขนาด 22.3Q/631L Black Glass Door รุ่น RT37GPSBB ระบบ Inverter แผงควบคุมดิจิตอล ราคา 21892.00 บาท</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VDsGZpKo0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823p6-moyuz7r6xclnae.webp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>116</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ปลั๊กสามตา ไฟ 10A 2500W ทนความร้อนได้ 750องศา Universal Adapter ราคา 143.00 บาท</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/70Hbfig4Bv</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0m-mchn1vs61k3k96.webp</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SHARP เครื่องฟอกอากาศ รุ่น FP-J30TA/B สีขาว-ดำ ราคา 4190.00 บาท</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Uyt8STEkC</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-8261b-mm8xye7fj94xe2.webp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>106</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ เครื่องทําไอศครีม1800W ไอศครีมโฮมเมดเครื่องทำไอศครีมสด ความจุ 9L ราคา 25487.00 บาท</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8ATZ3qGeJm</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp1o443u9s01aa.webp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>35</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LG เครื่องซักผ้า 14 กิโล รุ่นTT14NARG.DBMPETH เครื่องซักผ้า 2 ถัง ราคา 6890.00 บาท</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9fIMqQBjsd</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzu0ootarl4985.webp</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:50</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3185,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "A", "F", "C", "D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว"], "last_roles": ["R4", "R5", "R5", "R4", "R2", "R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น กริ่งประตูไร้สายพร้อมกล้องและอินเตอร์คอม ออดว ราคาแค่ 1304 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง นมโปรตีน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิท ราคาแค่ 177 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Flash Sale D เครื่องฟอกอากาศกรองpm2.5ขนสัตว์ ราคาแค่ 19800 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง TCL ตู้เย็น Free Builtin ราคาแค่ 29090 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3147,16 +3147,141 @@
           <t>https://s.shopee.co.th/9fIMqQBjsd</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lzu0ootarl4985.webp</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>done 2026-06-22 05:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>37</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>[NEW 2026] TCL ทีวี 65 นิ้ว 4K RGB Mini LED Google TV รุ่น 65Q7D HVA Pro Panel เหนือชั้นด้านสีสัน เก็บครบทุกรายละเอียด ราคา 44090.00 บาท</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/50WXHqlW3u</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823qi-moyuyzyqo4qpb7.webp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>9</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ABL LED TV 43" แอลอีดี ทีวี 43 นิ้ว สมาร์ททีวี ทีวีดิจิตอล ความละเอียด Full HD เสียงดัง คมชัด ราคา 4299.00 บาท</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V6PSDLRJL</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98o-lla4aab2op1aa6.webp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>87</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ระบบ อินเวอร์เตอร์ มี 4 ขนาด ตั้งแต่ 9200-24000 BTU แอร์บ้าน ผ่อน 0% ราคา 11871.00 บาท</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1Vwf7XmOe5</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-ml3dgcvreo02bf.webp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>86</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TOSHIBA ตู้เย็นมินิบาร์ ความจุ 3.1 คิว รุ่น GR-D906 ราคา 4408.00 บาท</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Ab1rxGmrW</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cf4b373a51935b28d3f9836eba4d0fbd.webp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>72</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>【เก็บปลายทาง】AOYANG Smart MPPT Solar Charge Controller ไฮโวลโซล่าชาร์เจอร์ 12-192 Volt AUTO รับไฟ PV ได้ 480V Max ราคา 2970.00 บาท</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5ApxUF8EFA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lyc2wsv0ae0x03.webp</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>done 2026-06-22 05:54</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3310,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "D", "G", "G", "D", "B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "การบอกต่อเฉยๆ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R8", "R7", "R8", "R4", "R6", "R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL แอร์ Full DC ราคาแค่ 18022 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น NEW TCL TV รุ่น ราคาแค่ 9690 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม บล็อ ราคาแค่ 79 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ รุ่นใหม่ล่าสุด เครื่องทำน้ำแข็ง อัตโนมัติ ice ราคาแค่ 2890 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ทีวีตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense ทีวี รุ่น ″ ราคาแค่ 10706 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม"], "last_roles": ["R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3272,16 +3272,141 @@
           <t>https://s.shopee.co.th/5ApxUF8EFA</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98v-lyc2wsv0ae0x03.webp</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>done 2026-06-22 05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>114</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FOTILE เครื่องดูดควันกระโจม JQG9009T 90 ซม. + เตาแก๊ส GHG78211 78 ซม. 2 หัวแก๊ส กำลังไฟ 5000 วัตต์ ราคา 34900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5JuiZ64</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134211-7r98y-lm2si4gb2xse7e.webp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>66</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูมิแบบอิสระ หม้อชาบู 6.5 L หม้อชาบู 2 ช่องต้ม ราคา 799.00 บาท</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2BCLuiapM1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-miv8q6eknabnf9.webp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>28</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>(Online Exclusive) Tefal เตารีดแรงดันไอน้ำ แรงดัน 6 บาร์ SV4210T0 STEAM STATION EXPRESS OPTIMAL 6 bar SV4210T0 ราคา 3270.00 บาท</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5L9NgRSdiW</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823om-mozovy2c0f0tc8.webp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>105</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>[จัดส่งฟรี] SAMSUNG 55 นิ้ว OLED S95F 4K Tizen OS SMART AI TV (2025) S95F Series รุ่น QA55S95FAKXXT ราคา 63490.00 บาท</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5JtWawz</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823p4-mp2ixeujype3d6.webp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>[NEW 2025] TCL ทีวี 98 นิ้ว 4K Mini QLED Google TV รุ่น 98Q6C HVA Panel,Gaming TV,IMAX Enhanced,120 Hz,VRR 288 Hz ราคา 75990.00 บาท</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/6AiUgDIeUC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rh-moyuz72j29kwc0.webp</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>done 2026-06-23 06:07</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3435,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "G", "G", "C", "G", "G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "มุกตลก", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม"], "last_roles": ["R3", "R6", "R1", "R7", "R7", "R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น พัดลม Hatari พัดลมอุตสาหกรรม นิ้ว ราคาแค่ 2598 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Prisma LED TV Digital ราคาแค่ 2190 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW Roborock Saros | ราคาแค่ 39090 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ทีวีตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ NEW TCL ทีวี นิ้ว ราคาแค่ 25290 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Tineco Floor One Station ราคาแค่ 25799 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3397,16 +3397,141 @@
           <t>https://s.shopee.co.th/6AiUgDIeUC</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823rh-moyuz72j29kwc0.webp</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>done 2026-06-23 06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>19</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>LJP 40L / 50L / 60L / 70Lพัดลมไอเย็น Air Cooler พัดลมไอน้ํา ปริมาณอากาศขนาดใหญ่ คุณภาพดี ใหญ่ การจัดส่งในประเทศไทย ราคา 1699.00 บาท</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5Jg6QgX</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0r-mbz03n96txwn00.webp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>25</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Hisense ทีวี รุ่น 75E7Q ขนาด 75 นิ้ว QLED 4K Ultra HD Smart TV Vidaa OS Wi-Fi รุ่น E7Q ราคา 20679.00 บาท</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8cVXAseU</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mp5izoio8nb5db.webp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>97</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Hisense TV 85 นิ้ว รุ่น 85E6Q 4K Ultra HD WCG MEMC VIDAA Smart TV Voice Control ราคา 26355.00 บาท</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5eHWmTal</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mp5iyeaf3yfj45.webp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Toshiba TV 75M450RP ทีวี 75 นิ้ว 4K Ultra HD Quantum Dot VIDAA HDR10+ Dolby Atmos Smart TV ราคา 30790.00 บาท</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LVm78XZUS</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mhtugkv3i9l4b7.webp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>55</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>[2026] iFFALCON iECO Series ขนาด 9,200–23,900 BTU แอร์ Inverter เย็นเร็ว ประหยัดไฟ ปรับแรงลม 7 ระดับ พร้อม Self Cleaning ราคา 9355.00 บาท</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/W47vcqqef</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pn-moyuz162pg5o39.webp</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:52</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3560,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "D", "B", "H", "B", "G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "มุกตลก", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "มุกตลก", "มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R5", "R2", "R5", "R4", "R5", "R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3"], "recent_captions": ["อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน ปี เตารีดแบบพกพาแบบพับได้ เตารีดแบบใช้ ราคาแค่ 246 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ HAIER แอร์ ขนาด , ราคาแค่ 27328 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก แวะมาแชร์ ทีวี ดีๆครับ ตัวนี้มีจุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 4990 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สินค้าตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ทักแชทก่อนสั่งซื้อ โปรx6.⚡️ส่วนลดคุ้มที่สุด 7 ราคาแค่ 73 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3522,16 +3522,141 @@
           <t>https://s.shopee.co.th/W47vcqqef</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823pn-moyuz162pg5o39.webp</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>done 2026-06-24 05:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>43</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>[แถมฟรี! ตู้เย็น รุ่น ER45B] Hisense DRYER Heat Pump เครื่องอบผ้าฝาหน้า 8 kg. สีเทา รุ่น DH80N1 ราคา 14372.00 บาท</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7Ab1rqoH80</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mp5iq16zykn5f5.webp</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>46</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด อาหารปลาอเนกประสงค์ เครื่องบดละเอียด บด ข้าวโพด บดแกลบ บดอาหารสัตว์ ขนาด มอ ราคา 4488.00 บาท</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/LkhjIeTuD</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-moatiudz1ukva4.webp</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Toshiba TV 55E330RP ทีวี 55 นิ้ว 4K Ultra HD Wifi HDR10 Voice Control Smart TV ราคา 11040.00 บาท</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5JeC38A</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mgn5hdwg1xje1b.webp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>29</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NEW 2026 SHARP TV 65 นิ้ว 4K UHD Google TV สมาร์ททีวี รุ่น 4T-C65FH320X (รับประกัน 3 ปี) ราคา 16900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3g19hNgtF9</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mp2g2pt3bwgc31.webp</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>32</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโทรล APP ควบคุม Night Vision &amp; Voice Change ระบบรักษาความปลอดภัยบ้านอัจฉริยะ ราคา 869.00 บาท</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8cVYCKiP</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-lqiuhgx3ja5x71.webp</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>done 2026-06-24 05:57</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3685,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "E", "E", "C", "G", "D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["มุกตลก", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R7", "R4", "R1", "R3", "R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tefal เตารีดแรงดันไอน้ำพลังสูง PRO EXPRESS ราคาแค่ 21568 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที\nหน้าร้อนเมืองไทยนี่มันร้อนจริง ๆ นะครับ ใครเคยเป็นบ้างที่อยากได้น้ำแข็งมาใส่เครื่องดื่มเย็น ๆ ดับกระหายแบบทันใจ แต่ในตู้เย็นก็ไม่พอหรือไม่ก็ต้องรอน้ำแข็งทำ? ผมเองก็เจอปัญหานี้บ่อย ๆ จนได้มาเจอ *สินค้า* ที่เป็นเครื่องทำน้ำแข็งอัตโนมัติรุ่นใหม่ล่าสุดเนี่ยแหละครับ เข้ามาช่วยชีวิตเลย คือไม่ต้องรอเลย แค่กดก็ได้น้ำแข็งแล้ว ตั้งแต่มีเจ้าเครื่องนี้ ชีวิตมันง่ายขึ้นเยอะเลยครับ ค่าตัวน้องอยู่ที่ 2890 บาท ถือว่าได้ความสะดวกสบายกลับมาเต็ม ๆ ครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น รับประกันศูนย์ไทย ปี Xiaomi Smart ราคาแค่ 2340 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง เครื่องอบลมร้อน ความจุ ไฟ รุ่นMV- ราคาแค่ 699 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HISENSE เครื่องซักผ้าฝาหน้า . กก. ราคาแค่ 11270 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก"], "last_roles": ["R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3647,16 +3647,141 @@
           <t>https://s.shopee.co.th/2g8cVYCKiP</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-lqiuhgx3ja5x71.webp</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>done 2026-06-24 05:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>69</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TCL RGB MiniLED 4K Google TV ขนาด 65-75 นิ้ว รุ่น Q7D 144Hz VRR มาพร้อมAiPQ Processor ลำโพงOnkyo2.1 ราคา 35590.00 บาท</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VaGh0nwX5</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/sg-11134201-823q1-mozm2dixwwzl9c.webp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>60</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>[ของแท้] BISSELL CrossWave Pet Pro เครื่องดูดฝุ่นถูพื้น 3in1 ดูด ล้าง เช็ดแห้ง แบบมีสาย ราคา 17599.00 บาท</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2g8cVcQb57</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mlzvvlnyi1vp74.webp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>104</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>[รับประกัน 1 ปี] เครื่องดูดฝุ่นในรถยนต์ เครื่องดูดฝุ่นไร้สาย แรงดูดสูง 99000Pa เครื่องดูดฝุ่นพกพา ชาร์จUSB ส่งด่วนจากไทย ราคา 199.00 บาท</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4ftgtPBcPD</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mmze5hm4pfr8b5.webp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>47</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>แบตเตอรี่โซล่าเซลล์ แบตเจล12v55ah แบตโซลาร์เซลล์ แบตเตอรี่12v โซล่าเซลล์ มีการรับประกัน แบตเตอรี่เจล Deep Cycle NPP ราคา 2499.00 บาท</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/110OWWkwu1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98u-lom8jv371ecfaf.webp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>48</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Airdog X8proUltra (D)เครื่องฟอกอากาศ ฝุ่นPM 2.5 ฆ่าเชื้อไวรัส ขนสัตว์ ฟอร์มาลดีไฮด์พื้นที่ 60-120 ตร.ม ราคา 60900.00 บาท</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/1gG5Jkrcge</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp1pzvpga5u7af.webp</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>done 2026-07-18 19:40</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3810,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "B", "D", "E", "H", "H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก"], "last_roles": ["R2", "R5", "R1", "R6", "R6", "R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Toshiba TV ทีวี นิ้ว ราคาแค่ 23790 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense TV รุ่น ทีวี ราคาแค่ 14040 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น โปรx5🔥🩵ส่วนลด 7เดือนแรก🩵 เครื่องกรองน้ำcoway  ราคาแค่ 199 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ESUN เครื่องทำน้ำแข็ง Ice maker ราคาแค่ 2450 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Candy เครื่องซักอบผ้าฝาหน้า ซักอบ ประหยัดไฟ ราคาแค่ 10950 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3772,16 +3772,41 @@
           <t>https://s.shopee.co.th/1gG5Jkrcge</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zth-mp1pzvpga5u7af.webp</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>done 2026-07-18 19:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>299</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>🫘ธัญพืชรวม 9 เซียน 500 กรัม ไม่ใส่เนย ไม่ใส่น้ำตาล รสธรรมชาติ อบใหม่ทุกวัน ราคา 179 บาท</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/5q5QhQsIk6</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgg2sb4dc1l899.webp</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>done 2026-07-23 20:12</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3835,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม"], "last_roles": ["R8", "R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง แอร์ HAIER INVERTER รุ่น ราคาแค่ 11899 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["A", "A", "B", "A", "F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "A"], "last_hooks": ["โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "คำถาม", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R3", "R2", "R5", "R1", "R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R5"], "recent_captions": ["โดนป้ายยามาอีกที ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 11871 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ติดตั้งฟรีทั่วไทย HAIER INVERTER รับประกันศูน ราคาแค่ 16890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ของกินตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ BENO เครื่องชงกาแฟเอสเพรสโซ่ รุ่น PRO-FLEX ราคาแค่ 18462 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของใช้สัตว์เลี้ยง ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น PETX FRESH BOX V. ราคาแค่ 3990 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี เวลาอยากหาขนมกินเล่นนั่งเคี้ยวตอนทำงาน แต่ไปเจอแบบที่เคลือบน้ำตาลหวานจัดหรือเยิ้มเนยจนอึดอัดรำคาญใจ ผมเลยลองสั่งธัญพืชรวมขนาด 500g ที่อบใหม่ รสธรรมชาติแท้ๆ แบบไม่ใส่เนยและไม่ใส่น้ำตาลมาลอง ในราคา 179 บาท เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ชอบหาของกินเล่นไว้ติดโต๊ะทำงานได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="630" yWindow="615" windowWidth="37095" windowHeight="17310" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -540,8 +540,6 @@
           <t>https://s.lazada.co.th/s.Z6hfCh?c=b&amp;t=p-i657CSw-sPs3l62</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3" ht="345" customHeight="1">
       <c r="A3" t="n">
@@ -562,8 +560,6 @@
           <t>https://s.lazada.co.th/s.Z6hUdg?c=a&amp;t=p-i6LWBD5-sR1psZs</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4" ht="409.5" customHeight="1">
       <c r="A4" t="n">
@@ -584,8 +580,6 @@
           <t>https://s.lazada.co.th/s.Z6hU5a?c=a&amp;t=p-i6Gn16K-s2Du0p2L</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -606,8 +600,6 @@
           <t>https://s.lazada.co.th/s.Z6hUQb?c=b</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -628,8 +620,6 @@
           <t>https://s.lazada.co.th/s.Z6hUp1?c=a&amp;t=p-i56HFEE-sPV7YBu</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -650,8 +640,6 @@
           <t>https://s.lazada.co.th/s.Z6hUs6?c=b&amp;t=p-i3IVVvd-sC7YM7H</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -672,8 +660,6 @@
           <t>https://s.lazada.co.th/s.Z6hUwm?c=b&amp;t=p-i3uxMq8-sFezCsD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -694,8 +680,6 @@
           <t>https://s.lazada.co.th/s.Z6hUBK?c=a&amp;t=p-i69orjh-sQEG95F</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -716,8 +700,6 @@
           <t>https://s.lazada.co.th/s.Z6po89?c=a&amp;t=p-i5UANgd-sNC8zX0</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -738,8 +720,6 @@
           <t>https://s.lazada.co.th/s.Z6poow?c=a&amp;t=p-i6YOKrQ-sSFykLR</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -760,8 +740,6 @@
           <t>https://s.lazada.co.th/s.Z6poHW?t=p-iHYzWWS-s2EM8tAv</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -782,8 +760,6 @@
           <t>https://s.lazada.co.th/s.Z6poC8?c=b&amp;t=p-i2Xh0Lf-sQBAMgv</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -804,8 +780,6 @@
           <t>https://s.lazada.co.th/s.Z6pL0t?c=b&amp;t=p-i6SvdvJ-sRgXbld</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -826,8 +800,6 @@
           <t>https://s.lazada.co.th/s.Z6pL38?c=b&amp;t=p-iJ4zNe-sV3TtR</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -848,8 +820,6 @@
           <t>https://s.lazada.co.th/s.Z6pL7d?c=a&amp;t=p-i2qXX8u-sAvS9sD</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -870,8 +840,6 @@
           <t>https://s.lazada.co.th/s.Z6pLoQ?c=b&amp;t=p-i6XgnuV-sSKIzpC</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -892,8 +860,6 @@
           <t>xxx</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -914,8 +880,6 @@
           <t>xxx</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -936,8 +900,6 @@
           <t>xxx</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -958,8 +920,6 @@
           <t>xxx</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -980,8 +940,6 @@
           <t>xxx</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -997,9 +955,6 @@
           <t>https://s.shopee.co.th/7VEfFsvKaC</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1015,9 +970,6 @@
           <t>https://s.shopee.co.th/1BKbiFSaJe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1033,9 +985,6 @@
           <t>https://s.shopee.co.th/80AvqoGO9N</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1051,9 +1000,6 @@
           <t>https://s.shopee.co.th/30mFtchbVD</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1069,9 +1015,6 @@
           <t>https://s.shopee.co.th/2LWZ6OswQB</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1087,9 +1030,6 @@
           <t>https://s.shopee.co.th/9fJ9pseQfr</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1105,9 +1045,6 @@
           <t>https://s.shopee.co.th/7VEfFu4YGN</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1123,9 +1060,6 @@
           <t>https://s.shopee.co.th/1qaIVUhisT</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1141,9 +1075,6 @@
           <t>https://s.shopee.co.th/AUsGpQNn7J</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1159,9 +1090,6 @@
           <t>https://s.shopee.co.th/20tihoBGes</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1177,9 +1105,6 @@
           <t>https://s.shopee.co.th/70IOf0AS0z</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1195,9 +1120,6 @@
           <t>https://s.shopee.co.th/4fuTsiaeol</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1213,9 +1135,6 @@
           <t>https://s.shopee.co.th/1VxS6u3tna</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1231,9 +1150,6 @@
           <t>https://s.shopee.co.th/qhlJgO6Xm</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1249,9 +1165,6 @@
           <t>https://s.shopee.co.th/AAFQQq6vcz</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1267,9 +1180,6 @@
           <t>https://s.shopee.co.th/1qaIVWus1e</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1285,9 +1195,6 @@
           <t>https://s.shopee.co.th/9zw0EXbwrg</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1303,9 +1210,6 @@
           <t>https://s.shopee.co.th/8pk2qOxe3x</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1321,9 +1225,6 @@
           <t>https://s.shopee.co.th/qhlJhh5Rx</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1339,9 +1240,6 @@
           <t>https://s.shopee.co.th/6VM847bfaQ</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1357,9 +1255,6 @@
           <t>https://s.shopee.co.th/9AMtF2HyEz</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1375,9 +1270,6 @@
           <t>https://s.shopee.co.th/5VTasInfKp</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1393,9 +1285,6 @@
           <t>https://s.shopee.co.th/2VpzInGTld</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1411,9 +1300,6 @@
           <t>https://s.shopee.co.th/3g1wgxG6QW</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1429,9 +1315,6 @@
           <t>https://s.shopee.co.th/18eKDdCj1</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1447,9 +1330,6 @@
           <t>https://s.shopee.co.th/8fQce9KRPW</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1465,9 +1345,6 @@
           <t>https://s.shopee.co.th/40en5Znxih</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1483,9 +1360,6 @@
           <t>https://s.shopee.co.th/1BKbiNBwrB</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1501,9 +1375,6 @@
           <t>https://s.shopee.co.th/qhlJlVdlh</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1519,9 +1390,6 @@
           <t>https://s.shopee.co.th/7fY5SKITwI</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1537,9 +1405,6 @@
           <t>https://s.shopee.co.th/AUsGpXCRHn</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1555,9 +1420,6 @@
           <t>https://s.shopee.co.th/AUsGpXLrDC</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1573,9 +1435,6 @@
           <t>https://s.shopee.co.th/2BD8uE3XkP</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1591,9 +1450,6 @@
           <t>https://s.shopee.co.th/3ViWUgC0hc</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1609,9 +1465,6 @@
           <t>https://s.shopee.co.th/7AborQ6MzS</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1627,9 +1480,6 @@
           <t>https://s.shopee.co.th/4AyDHuWMgW</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1645,9 +1495,6 @@
           <t>https://s.shopee.co.th/4fuTspglce</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1663,9 +1510,6 @@
           <t>https://s.shopee.co.th/9UzjdibQbo</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1681,9 +1525,6 @@
           <t>https://s.shopee.co.th/2g9PVA9gwT</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1699,9 +1540,6 @@
           <t>https://s.shopee.co.th/80AvqycbsM</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1717,9 +1555,6 @@
           <t>https://s.shopee.co.th/3g1wh15cOS</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1735,9 +1570,6 @@
           <t>https://s.shopee.co.th/2VpzIsNfgG</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1753,9 +1585,6 @@
           <t>https://s.shopee.co.th/18eKHkSMZ</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1771,9 +1600,6 @@
           <t>https://s.shopee.co.th/9UzjdkOrgx</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1789,9 +1615,6 @@
           <t>https://s.shopee.co.th/6L2hrvmTAf</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1807,9 +1630,6 @@
           <t>https://s.shopee.co.th/18eKIO7gN</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1825,9 +1645,6 @@
           <t>https://s.shopee.co.th/7AborTBLSP</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1843,9 +1660,6 @@
           <t>https://s.shopee.co.th/4qDu5BX0y0</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1861,9 +1675,6 @@
           <t>https://s.shopee.co.th/8AUM3JW52j</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1879,9 +1690,6 @@
           <t>https://s.shopee.co.th/5fn14j6PNu</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1897,9 +1705,6 @@
           <t>https://s.shopee.co.th/1BKbiSasOl</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1915,9 +1720,6 @@
           <t>https://s.shopee.co.th/9AMtFAFDjS</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1933,9 +1735,6 @@
           <t>https://s.shopee.co.th/7VEfG6YDLk</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1951,9 +1750,6 @@
           <t>https://s.shopee.co.th/AAFQR0Wiym</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1969,9 +1765,6 @@
           <t>https://s.shopee.co.th/6L2hrxz8Sx</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1987,9 +1780,6 @@
           <t>https://s.shopee.co.th/9Uzjdn0UBp</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2005,9 +1795,6 @@
           <t>https://s.shopee.co.th/6VM84HLsHn</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2023,9 +1810,6 @@
           <t>https://s.shopee.co.th/LlUiwutrg</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2041,9 +1825,6 @@
           <t>https://s.shopee.co.th/4LHdUJNSmG</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2059,9 +1840,6 @@
           <t>https://s.shopee.co.th/20tii1jc7S</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2077,9 +1855,6 @@
           <t>https://s.shopee.co.th/8pk2qaXHRu</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2095,9 +1870,6 @@
           <t>https://s.shopee.co.th/18eKMJ07G</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2113,9 +1885,6 @@
           <t>https://s.shopee.co.th/AUsGpen4VE</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2131,9 +1900,6 @@
           <t>https://s.shopee.co.th/3LP6IUMSzy</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2149,9 +1915,6 @@
           <t>https://s.shopee.co.th/6L2hs0KKI1</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2167,8 +1930,6 @@
           <t>https://s.shopee.co.th/80Avr4O9iM</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>฿245</t>
@@ -2189,9 +1950,6 @@
           <t>https://s.shopee.co.th/5VTasTa9F8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2207,9 +1965,6 @@
           <t>https://s.shopee.co.th/8fQceIXVjD</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2225,9 +1980,6 @@
           <t>https://s.shopee.co.th/7prVelivtr</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2243,9 +1995,6 @@
           <t>https://s.shopee.co.th/30mFtt9zja</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2261,9 +2010,6 @@
           <t>https://s.shopee.co.th/3g1wh7BvQY</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2279,9 +2025,6 @@
           <t>https://s.shopee.co.th/5AqkTsF9TH</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2297,9 +2040,6 @@
           <t>https://s.shopee.co.th/2BD8uMUpoj</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2315,9 +2055,6 @@
           <t>https://s.shopee.co.th/AAFQR496sz</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2333,9 +2070,6 @@
           <t>https://s.shopee.co.th/5AqkTsX5uh</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2351,9 +2085,6 @@
           <t>https://s.shopee.co.th/3LP6IVnu89</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2369,9 +2100,6 @@
           <t>https://s.shopee.co.th/40en5joK4K</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2387,9 +2115,6 @@
           <t>https://s.shopee.co.th/2BD8uN4eS8</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2405,9 +2130,6 @@
           <t>https://s.shopee.co.th/4fuTsyQCuy</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2423,9 +2145,6 @@
           <t>https://s.shopee.co.th/5AqkTtWU54</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2441,9 +2160,6 @@
           <t>https://s.shopee.co.th/3ViWUplu4m</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2459,9 +2175,6 @@
           <t>https://s.shopee.co.th/7AborZbvqc</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2477,9 +2190,6 @@
           <t>https://s.shopee.co.th/6L2hs2t3na</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2495,9 +2205,6 @@
           <t>https://s.shopee.co.th/9KgJRYuUig</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2513,9 +2220,6 @@
           <t>https://s.shopee.co.th/3g1wh9Udp3</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2531,9 +2235,6 @@
           <t>https://s.shopee.co.th/1qaIVmiZ0z</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2549,9 +2250,6 @@
           <t>https://s.shopee.co.th/3ViWUqppYR</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2567,9 +2265,6 @@
           <t>https://s.shopee.co.th/4fuTszzcT5</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2585,8 +2280,6 @@
           <t>https://s.shopee.co.th/9fJ9qBnnrE</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>฿195</t>
@@ -2607,9 +2300,6 @@
           <t>https://s.shopee.co.th/8KnmFk6hHc</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2625,9 +2315,6 @@
           <t>https://s.shopee.co.th/4qDu5JXZ2c</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2643,9 +2330,6 @@
           <t>https://s.shopee.co.th/6VM84NmSg0</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2661,9 +2345,6 @@
           <t>https://s.shopee.co.th/9fJ9qCkzez</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2679,9 +2360,6 @@
           <t>https://s.shopee.co.th/6L2hs58xPs</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2697,9 +2375,6 @@
           <t>https://s.shopee.co.th/8pk2qgE9Rg</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2715,8 +2390,6 @@
           <t>https://s.shopee.co.th/2g9PVLpEtN</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>฿275</t>
@@ -2737,9 +2410,6 @@
           <t>https://s.shopee.co.th/1BKbhWFl4X</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2755,9 +2425,6 @@
           <t>https://s.shopee.co.th/3g1wg7FaeC</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2773,9 +2440,6 @@
           <t>https://s.shopee.co.th/BS4VgbEUZ</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2791,9 +2455,6 @@
           <t>https://s.shopee.co.th/50XKGZSFb2</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2809,9 +2470,6 @@
           <t>https://s.shopee.co.th/7AboqYTyDv</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2827,9 +2485,6 @@
           <t>https://s.shopee.co.th/9pca1SVZeY</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2845,9 +2500,6 @@
           <t>https://s.shopee.co.th/3g1wg8BgFC</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2863,9 +2515,6 @@
           <t>https://s.shopee.co.th/40en4kQQez</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2881,9 +2530,6 @@
           <t>https://s.shopee.co.th/5VTarVcSGK</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2899,9 +2545,6 @@
           <t>https://s.shopee.co.th/7prVdnlExh</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2917,9 +2560,6 @@
           <t>https://s.shopee.co.th/7VEfFC3yDF</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2935,9 +2575,6 @@
           <t>https://s.shopee.co.th/6VM83MPNMl</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2953,9 +2590,6 @@
           <t>https://s.shopee.co.th/2LWZ5hsv02</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2971,9 +2605,6 @@
           <t>https://s.shopee.co.th/2BD8tPAwgQ</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2989,9 +2620,6 @@
           <t>https://s.shopee.co.th/5q6RG9En9w</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3007,9 +2635,6 @@
           <t>https://s.shopee.co.th/4qDu4JaGa6</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3025,9 +2650,6 @@
           <t>https://s.shopee.co.th/9pca1VZAtx</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3043,9 +2665,6 @@
           <t>https://s.shopee.co.th/1VxS6CHCkA</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3061,9 +2680,6 @@
           <t>https://s.shopee.co.th/8pk2pg4PXC</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3079,9 +2695,6 @@
           <t>https://s.shopee.co.th/7prVdqOVjk</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3097,9 +2710,6 @@
           <t>https://s.shopee.co.th/60PrSUHkWD</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3115,9 +2725,6 @@
           <t>https://s.shopee.co.th/18eJSxDmH</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3133,9 +2740,6 @@
           <t>https://s.shopee.co.th/6ffYFioThF</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3151,9 +2755,6 @@
           <t>https://s.shopee.co.th/80AvqB1xnA</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3169,9 +2770,6 @@
           <t>https://s.shopee.co.th/5q6RGCSDsU</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3187,9 +2785,6 @@
           <t>https://s.shopee.co.th/7VEfFGc6Nl</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3205,9 +2800,6 @@
           <t>https://s.shopee.co.th/40en4q2YZI</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3223,9 +2815,6 @@
           <t>https://s.shopee.co.th/8AUM2UzLOt</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3241,9 +2830,6 @@
           <t>https://s.shopee.co.th/7VEfFHL3sV</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3259,9 +2845,6 @@
           <t>https://s.shopee.co.th/8KnmEoUKef</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3277,9 +2860,6 @@
           <t>https://s.shopee.co.th/2BD8tU4jTW</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3295,9 +2875,6 @@
           <t>https://s.shopee.co.th/4fuTs5D5ZL</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3313,9 +2890,6 @@
           <t>https://s.shopee.co.th/9KgJQfD3lX</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3331,9 +2905,6 @@
           <t>https://s.shopee.co.th/gOL6jxFhW</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3349,9 +2920,6 @@
           <t>https://s.shopee.co.th/9KgJQfhrEY</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3367,9 +2935,6 @@
           <t>https://s.shopee.co.th/40en4sGOKp</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3385,9 +2950,6 @@
           <t>https://s.shopee.co.th/2qSpgjc1G6</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3403,9 +2965,6 @@
           <t>https://s.shopee.co.th/9fJ9pISqdb</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3421,9 +2980,6 @@
           <t>https://s.shopee.co.th/4LHdTV4c5m</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3439,9 +2995,6 @@
           <t>https://s.shopee.co.th/8pk2pm4Wy8</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3457,9 +3010,6 @@
           <t>https://s.shopee.co.th/8fQcdTwmqO</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3475,9 +3025,6 @@
           <t>https://s.shopee.co.th/6VM83VLfhL</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3493,9 +3040,6 @@
           <t>https://s.shopee.co.th/3qLMsbo2b9</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3511,9 +3055,6 @@
           <t>https://s.shopee.co.th/2BD8tYCKR4</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3529,9 +3070,6 @@
           <t>https://s.shopee.co.th/20tihFYLJP</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3547,9 +3085,6 @@
           <t>https://s.shopee.co.th/60PrSbaVXX</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3565,9 +3100,6 @@
           <t>https://s.shopee.co.th/2qSpgn41bw</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3583,9 +3115,6 @@
           <t>https://s.shopee.co.th/4fuTsAAaVe</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3601,9 +3130,6 @@
           <t>https://s.shopee.co.th/2qSpgnYtJH</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3619,9 +3145,6 @@
           <t>https://s.shopee.co.th/8fQcdWUHbe</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3637,9 +3160,6 @@
           <t>https://s.shopee.co.th/903T292h1r</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3655,9 +3175,6 @@
           <t>https://s.shopee.co.th/5fn141SrBX</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3673,9 +3190,6 @@
           <t>https://s.shopee.co.th/6ffYFrhokq</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3691,9 +3205,6 @@
           <t>https://s.shopee.co.th/9fJ9pNm0BD</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3709,9 +3220,6 @@
           <t>https://s.shopee.co.th/4LHdTaOFRa</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3727,9 +3235,6 @@
           <t>https://s.shopee.co.th/9pca1hLBSl</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3745,9 +3250,6 @@
           <t>https://s.shopee.co.th/8pk2prgJaW</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3763,9 +3265,6 @@
           <t>https://s.shopee.co.th/AKYqccp2br</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3781,9 +3280,6 @@
           <t>https://s.shopee.co.th/9fJ9pP7fJG</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3799,9 +3295,6 @@
           <t>https://s.shopee.co.th/3ViWU5MDIq</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3817,9 +3310,6 @@
           <t>https://s.shopee.co.th/AKYqceDWTl</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3835,9 +3325,6 @@
           <t>https://s.shopee.co.th/2qSpgrzbCy</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3853,9 +3340,6 @@
           <t>https://s.shopee.co.th/AKYqceiwJg</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3871,9 +3355,6 @@
           <t>https://s.shopee.co.th/111BVVZvrQ</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3889,9 +3370,6 @@
           <t>https://s.shopee.co.th/7prVe4MuYP</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3907,9 +3385,6 @@
           <t>https://s.shopee.co.th/BS4Vz2x96</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3925,9 +3400,6 @@
           <t>https://s.shopee.co.th/9AMtEWns3u</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3943,9 +3415,6 @@
           <t>https://s.shopee.co.th/3ViWU7PfSD</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3961,9 +3430,6 @@
           <t>https://s.shopee.co.th/3LP6Hoe7Td</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3979,9 +3445,6 @@
           <t>https://s.shopee.co.th/40en52odwn</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3997,9 +3460,6 @@
           <t>https://s.shopee.co.th/9pca1ly7zu</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4015,9 +3475,6 @@
           <t>https://s.shopee.co.th/AAFQQO91kT</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4033,9 +3490,6 @@
           <t>https://s.shopee.co.th/9pca1mVskZ</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4051,9 +3505,6 @@
           <t>https://s.shopee.co.th/8fQcddrvGJ</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4069,9 +3520,6 @@
           <t>https://s.shopee.co.th/4Vb3fzQpMi</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4087,9 +3535,6 @@
           <t>https://s.shopee.co.th/5LAAfWedQp</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4105,9 +3550,6 @@
           <t>https://s.shopee.co.th/LlUiLGId2</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4123,9 +3565,6 @@
           <t>https://s.shopee.co.th/4AyDHOmw07</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4141,9 +3580,6 @@
           <t>https://s.shopee.co.th/7prVe8rKaS</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4159,9 +3595,6 @@
           <t>https://s.shopee.co.th/60PrSmEwkn</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4177,9 +3610,6 @@
           <t>https://s.shopee.co.th/2qSpgxdvUb</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4195,9 +3625,6 @@
           <t>https://s.shopee.co.th/3ViWUBppDY</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4213,9 +3640,6 @@
           <t>https://s.shopee.co.th/18eJlLA00</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4231,9 +3655,6 @@
           <t>https://s.shopee.co.th/70IOed6gEM</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4249,9 +3670,6 @@
           <t>https://s.shopee.co.th/gOL6zn0ZU</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4267,9 +3685,6 @@
           <t>https://s.shopee.co.th/8KnmF5aSS6</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4285,9 +3700,6 @@
           <t>https://s.shopee.co.th/9fJ9pXn39G</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4303,9 +3715,6 @@
           <t>https://s.shopee.co.th/2BD8tlSwED</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4321,9 +3730,6 @@
           <t>https://s.shopee.co.th/AAFQQTAzin</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4339,9 +3745,6 @@
           <t>https://s.shopee.co.th/3qLMspmr2A</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4357,9 +3760,6 @@
           <t>https://s.shopee.co.th/18eJnJ2vU</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4375,9 +3775,6 @@
           <t>https://s.shopee.co.th/5q6RGWDt8R</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4393,9 +3790,6 @@
           <t>https://s.shopee.co.th/9zw0EBFUHg</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4411,9 +3805,6 @@
           <t>https://s.shopee.co.th/AUsGp7HeGo</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4429,9 +3820,6 @@
           <t>https://s.shopee.co.th/1VxS7D5qgi</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4447,9 +3835,6 @@
           <t>https://s.shopee.co.th/80AvrF15AH</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4465,9 +3850,6 @@
           <t>https://s.shopee.co.th/6AjHfsCBcG</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4483,9 +3865,6 @@
           <t>https://s.shopee.co.th/AKYqdX4Zec</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -4501,9 +3880,6 @@
           <t>https://s.shopee.co.th/80AvrFRLKb</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -4519,9 +3895,6 @@
           <t>https://s.shopee.co.th/1gGsJc2RlS</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -4537,9 +3910,6 @@
           <t>https://s.shopee.co.th/60PrTZyWw9</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -4555,9 +3925,6 @@
           <t>https://s.shopee.co.th/4AyDIDJfgl</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -4573,9 +3940,6 @@
           <t>https://s.shopee.co.th/9fJ9qKBaYO</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -4591,9 +3955,6 @@
           <t>https://s.shopee.co.th/3B5g6NkVbz</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -4609,9 +3970,6 @@
           <t>https://s.shopee.co.th/7fY5SeevTQ</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4627,9 +3985,6 @@
           <t>https://s.shopee.co.th/8KnmFspF9s</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4645,9 +4000,6 @@
           <t>https://s.shopee.co.th/AAFQRFvo6B</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4663,9 +4015,6 @@
           <t>https://s.shopee.co.th/6VM84WOCbh</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4681,9 +4030,6 @@
           <t>https://s.shopee.co.th/4fuTt9h8x5</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4699,9 +4045,6 @@
           <t>https://s.shopee.co.th/8KnmFtgrhB</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4717,9 +4060,6 @@
           <t>https://s.shopee.co.th/2VpzJBFRlB</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4735,9 +4075,6 @@
           <t>https://s.shopee.co.th/50XKHmL7f1</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4753,9 +4090,6 @@
           <t>https://s.shopee.co.th/AAFQRH9q9C</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4771,9 +4105,6 @@
           <t>https://s.shopee.co.th/9KgJRkOpwT</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4789,9 +4120,6 @@
           <t>https://s.shopee.co.th/1gGsJf5qBy</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4807,9 +4135,6 @@
           <t>https://s.shopee.co.th/AKYqdbKcqx</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4825,9 +4150,6 @@
           <t>https://s.shopee.co.th/4qDu5UscpA</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4843,9 +4165,6 @@
           <t>https://s.shopee.co.th/1qaIVzHJWM</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4861,9 +4180,6 @@
           <t>https://s.shopee.co.th/BS4WvciKX</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4879,9 +4195,6 @@
           <t>https://s.shopee.co.th/18eKcpF29</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4897,9 +4210,6 @@
           <t>https://s.shopee.co.th/5AqkU7idNK</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4915,9 +4225,6 @@
           <t>https://s.shopee.co.th/gOL7rCcXa</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4933,9 +4240,6 @@
           <t>https://s.shopee.co.th/5AqkU89AcS</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4951,9 +4255,6 @@
           <t>https://s.shopee.co.th/5AqkU8Qlij</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4969,9 +4270,6 @@
           <t>https://s.shopee.co.th/2LWZ6vkd5M</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4987,9 +4285,6 @@
           <t>https://s.shopee.co.th/40en5zqrhW</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5005,9 +4300,6 @@
           <t>https://s.shopee.co.th/7KvF47rr6x</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5023,9 +4315,6 @@
           <t>https://s.shopee.co.th/7prVf339Rs</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5041,9 +4330,6 @@
           <t>https://s.shopee.co.th/BS4Wxj3Y0</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5059,9 +4345,6 @@
           <t>https://s.shopee.co.th/2BD8udp7dW</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -5077,9 +4360,6 @@
           <t>https://s.shopee.co.th/AKYqdeWc3R</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -5095,9 +4375,6 @@
           <t>https://s.shopee.co.th/70IOfWsVyq</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -5113,9 +4390,6 @@
           <t>https://s.shopee.co.th/8KnmFz01FW</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -5131,9 +4405,6 @@
           <t>https://s.shopee.co.th/W4uvahaah</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -5149,9 +4420,6 @@
           <t>https://s.shopee.co.th/5LAAfiMAyZ</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -5167,9 +4435,6 @@
           <t>https://s.shopee.co.th/111BVkrJbg</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -5185,9 +4450,6 @@
           <t>https://s.shopee.co.th/gOL790Lut</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -5203,9 +4465,6 @@
           <t>https://s.shopee.co.th/111BVl7blo</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -5221,9 +4480,6 @@
           <t>https://s.shopee.co.th/3g1wgf6WxV</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -5239,9 +4495,6 @@
           <t>https://s.shopee.co.th/5AqkTQD7rt</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -5257,9 +4510,6 @@
           <t>https://s.shopee.co.th/gOL79hSKd</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -5275,9 +4525,6 @@
           <t>https://s.shopee.co.th/60PrSxVx5L</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -5293,9 +4540,6 @@
           <t>https://s.shopee.co.th/1BKbi51Tyt</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -5311,9 +4555,6 @@
           <t>https://s.shopee.co.th/W4uurLpFb</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -5329,9 +4570,6 @@
           <t>https://s.shopee.co.th/80AvqeBd2K</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -5347,9 +4585,6 @@
           <t>https://s.shopee.co.th/6L2hraUpS6</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -5365,9 +4600,6 @@
           <t>https://s.shopee.co.th/1Le1uP5fVx</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -5383,9 +4615,6 @@
           <t>https://s.shopee.co.th/5q6RGg5W9m</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -5401,9 +4630,6 @@
           <t>https://s.shopee.co.th/9KgJR76ldw</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -5419,9 +4645,6 @@
           <t>https://s.shopee.co.th/20tihdkvDF</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -5437,9 +4660,6 @@
           <t>https://s.shopee.co.th/7fY5S3gwpf</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -5455,9 +4675,6 @@
           <t>https://s.shopee.co.th/3B5g5nBHJB</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -5473,9 +4690,6 @@
           <t>https://s.shopee.co.th/AKYqcxsWHc</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -5491,9 +4705,6 @@
           <t>https://s.shopee.co.th/1VxS6jZ9Yl</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -5509,9 +4720,6 @@
           <t>https://s.shopee.co.th/6ffYGEokbC</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -5527,9 +4735,6 @@
           <t>https://s.shopee.co.th/2BD8tyE3wo</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -5545,9 +4750,6 @@
           <t>https://s.shopee.co.th/9UzjdRvdFe</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -5563,9 +4765,6 @@
           <t>https://s.shopee.co.th/20tihfWqV9</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -5581,9 +4780,6 @@
           <t>https://s.shopee.co.th/3g1wgjZZjV</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -5599,9 +4795,6 @@
           <t>https://s.shopee.co.th/9fJ9plKum9</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -5617,9 +4810,6 @@
           <t>https://s.shopee.co.th/8V7CRcd2JM</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -5635,9 +4825,6 @@
           <t>https://s.shopee.co.th/3ViWUR4OBe</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -5653,9 +4840,6 @@
           <t>https://s.shopee.co.th/8V7CRculy4</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -5671,9 +4855,6 @@
           <t>https://s.shopee.co.th/5AqkTVGOp9</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -5689,9 +4870,6 @@
           <t>https://s.shopee.co.th/2g9PUucyiO</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -5707,9 +4885,6 @@
           <t>https://s.shopee.co.th/BS4WJwSoe</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -5725,9 +4900,6 @@
           <t>https://s.shopee.co.th/7prVePfRfX</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -5743,9 +4915,6 @@
           <t>https://s.shopee.co.th/7AborBptBz</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5761,9 +4930,6 @@
           <t>https://s.shopee.co.th/9UzjdTuxft</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5779,9 +4945,6 @@
           <t>https://s.shopee.co.th/6ffYGHEgWP</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5797,9 +4960,6 @@
           <t>https://s.shopee.co.th/8pk2qGELGy</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5815,9 +4975,6 @@
           <t>https://s.shopee.co.th/8AUM32LLfg</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5833,7 +4990,6 @@
           <t>https://s.shopee.co.th/2LVYWybRCL</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moqjyxd47uvg21.webp</t>
@@ -5842,6 +4998,11 @@
       <c r="F291" t="inlineStr">
         <is>
           <t>฿68</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>done 2026-07-24 20:06</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5020,6 @@
           <t>https://s.shopee.co.th/3B4fWVcJyu</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98z-ls5bmhjwe8xpa2.webp</t>
@@ -5885,7 +5045,6 @@
           <t>https://s.shopee.co.th/4AxCiLiHBf</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-7reoj-m2ca7ylu2juga8.webp</t>
@@ -5911,7 +5070,6 @@
           <t>https://s.shopee.co.th/W3uLc4l8v</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasf-m7chjcgtfipr9f.webp</t>
@@ -5937,7 +5095,6 @@
           <t>https://s.shopee.co.th/9zuzf4cm4U</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m8n40uz26b5a24.webp</t>
@@ -5963,7 +5120,6 @@
           <t>https://s.shopee.co.th/7KuEUB54i6</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rash-m0o761t95wig4d.webp</t>
@@ -5989,7 +5145,6 @@
           <t>https://s.shopee.co.th/LkU9JmuTA</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mgw9302qykuj09.webp</t>
@@ -6015,7 +5170,6 @@
           <t>https://s.shopee.co.th/8ATLTiSIiJ</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-23020-fghif5jf3inveb.webp</t>
@@ -6041,7 +5195,6 @@
           <t>https://s.shopee.co.th/2VoyjIwfmE</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztg-mkkvkc7pmku8d4.webp</t>
@@ -6067,7 +5220,6 @@
           <t>https://s.shopee.co.th/5q5QhQsIk6</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgg2sb4dc1l899.webp</t>
@@ -6093,7 +5245,6 @@
           <t>https://s.shopee.co.th/2VoyjJMS7q</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rase-m8vqwsb7876o1f.webp</t>
@@ -6119,7 +5270,6 @@
           <t>https://s.shopee.co.th/7KuEUCNESu</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-820l4-mehzdrupcuteaf.webp</t>
@@ -6145,7 +5295,6 @@
           <t>https://s.shopee.co.th/30lnXsX9Lw</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-7rd63-m70pki5sxt3db3.webp</t>
@@ -6171,7 +5320,6 @@
           <t>https://s.shopee.co.th/AAEy53EnsA</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasl-m7dtemqzvjru7c.webp</t>
@@ -6197,7 +5345,6 @@
           <t>https://s.shopee.co.th/6ff5ucfwhL</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81zto-mo97h5l1bs3q29.webp</t>
@@ -6223,7 +5370,6 @@
           <t>https://s.shopee.co.th/3Vi48o02n1</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81zte-mos57zj9wmq7bb.webp</t>
@@ -6249,7 +5395,6 @@
           <t>https://s.shopee.co.th/1gGPxRFxbE</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztm-moxolsaaeh3416.webp</t>
@@ -6275,7 +5420,6 @@
           <t>https://s.shopee.co.th/Ll2MzThMP</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztk-mdyso1l1mbcz05.webp</t>
@@ -6301,7 +5445,6 @@
           <t>https://s.shopee.co.th/7fXd6TF7Kq</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m2kqhy2g61771f.webp</t>
@@ -6327,7 +5470,6 @@
           <t>https://s.shopee.co.th/70HwJFUr2O</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m6s568lain0797.webp</t>
@@ -6353,7 +5495,6 @@
           <t>https://s.shopee.co.th/AAEy54SM4R</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-7ra32-mbi09g90wacl3d.webp</t>
@@ -6379,7 +5520,6 @@
           <t>https://s.shopee.co.th/18ByODaD0</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0m-md07yr981fr416.webp</t>
@@ -6405,7 +5545,6 @@
           <t>https://s.shopee.co.th/8pjaUcokqa</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mpdbdc780q30f2.webp</t>
@@ -6431,7 +5570,6 @@
           <t>https://s.shopee.co.th/W4SZJSnUE</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztk-mpkz0ay83n5tef.webp</t>
@@ -6457,7 +5595,6 @@
           <t>https://s.shopee.co.th/2LW6kgUPXr</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-7rdxc-lxgiayq11js633.webp</t>
@@ -6483,7 +5620,6 @@
           <t>https://s.shopee.co.th/9UzHHrBzqG</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztl-mibu5xev4kjq01.webp</t>
@@ -6509,7 +5645,6 @@
           <t>https://s.shopee.co.th/Ll2N0uaP5</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mnmm1zeaeio658.webp</t>
@@ -6535,7 +5670,6 @@
           <t>https://s.shopee.co.th/BRcAi41JA</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mpkjmivwelfz69.webp</t>
@@ -6561,7 +5695,6 @@
           <t>https://s.shopee.co.th/3LOdwWzwJR</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasm-m13vjqfbtn3o49.webp</t>
@@ -6617,7 +5750,6 @@
           <t>https://s.shopee.co.th/7AbMVrSjRr</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mnmyv5cdh05e5b.webp</t>
@@ -6643,7 +5775,6 @@
           <t>https://s.shopee.co.th/1LdZZ95AAb</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztp-mngva2okzpjaca.webp</t>
@@ -6669,7 +5800,6 @@
           <t>https://s.shopee.co.th/8pjaUvq9ci</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mmfq4vxucrgla3.webp</t>
@@ -6695,7 +5825,6 @@
           <t>https://s.shopee.co.th/W4SZcVdkx</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7ra0h-mcpd1y74lysm7e.webp</t>
@@ -6721,7 +5850,6 @@
           <t>https://s.shopee.co.th/2BCgYgRq4z</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81zth-mmixuw8fz18i52.webp</t>
@@ -6747,7 +5875,6 @@
           <t>https://s.shopee.co.th/AAEy5OGUk8</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mni8oy7lbjer1f.webp</t>
@@ -6773,7 +5900,6 @@
           <t>https://s.shopee.co.th/8ATthiVwhF</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztn-mncpondjeg3nd1.webp</t>
@@ -6799,7 +5925,6 @@
           <t>https://s.shopee.co.th/5fmYj7nmUw</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lnfj2bxeyxioc3.webp</t>
@@ -6825,7 +5950,6 @@
           <t>https://s.shopee.co.th/6ff5uxshlo</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mn5j25gwgmx2ed.webp</t>
@@ -6851,7 +5975,6 @@
           <t>https://s.shopee.co.th/40eKk4DAW1</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7qula-lhkogxzv71yba0.webp</t>
@@ -6877,7 +6000,6 @@
           <t>https://s.shopee.co.th/6ff5uyAZwu</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztg-mm8rnpzzshs429.webp</t>
@@ -6903,7 +6025,6 @@
           <t>https://s.shopee.co.th/9030hGB78j</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98u-lyj1u7grm8w1bb.webp</t>
@@ -6929,7 +6050,6 @@
           <t>https://s.shopee.co.th/W4SZdljey</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztf-mm9msusd71fnbc.webp</t>
@@ -6955,7 +6075,6 @@
           <t>https://s.shopee.co.th/3B5DkXjty0</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98v-lp4vdgeuw77id2.webp</t>
@@ -6981,7 +6100,6 @@
           <t>https://s.shopee.co.th/4fu1XIoEEN</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztm-mgvmi6civ40e0a.webp</t>
@@ -7007,7 +6125,6 @@
           <t>https://s.shopee.co.th/3LOdwr0WRj</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rasg-m7hrtewsksjj0d.webp</t>
@@ -7033,7 +6150,6 @@
           <t>https://s.shopee.co.th/9030hGnxIf</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-81ztq-mo16o8447m69aa.webp</t>
@@ -7059,7 +6175,6 @@
           <t>https://s.shopee.co.th/4Axkw6V9mV</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mk0m1nqpb6rl65.webp</t>
@@ -7085,7 +6200,6 @@
           <t>https://s.shopee.co.th/5fmYird7uy</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-7rccb-lrk78gtun9kb25.webp</t>
@@ -7111,7 +6225,6 @@
           <t>https://s.shopee.co.th/W4SZNKAYm</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mpbmea7lcwel5d.webp</t>
@@ -7137,7 +6250,6 @@
           <t>https://s.shopee.co.th/7pr3IrQQ0Q</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7rase-m9na6e5euezk7a.webp</t>
@@ -7163,7 +6275,6 @@
           <t>https://s.shopee.co.th/9AMQtJPT2E</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98w-m002n9j8eqgxd8.webp</t>
@@ -7189,7 +6300,6 @@
           <t>https://s.shopee.co.th/5fmYisqstO</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/cn-11134207-820l4-mld5o6ty6juo43.webp</t>
@@ -7215,7 +6325,6 @@
           <t>https://s.shopee.co.th/60PP7UxWN7</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-8224r-mhol31jcaholea.webp</t>
@@ -7241,7 +6350,6 @@
           <t>https://s.shopee.co.th/4LHB8R99ws</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98p-lq9499no64tg95.webp</t>
@@ -7267,7 +6375,6 @@
           <t>https://s.shopee.co.th/AKYOHStbZL</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7r98o-lzhrgu8c0n8pfe.webp</t>
@@ -7293,7 +6400,6 @@
           <t>https://s.shopee.co.th/3qKuXWRuCs</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/th-11134207-7ras9-m66pbx8t6s2l68.webp</t>
@@ -7319,7 +6425,6 @@
           <t>https://s.shopee.co.th/1qZq9qj4iN</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
           <t>https://down-zl-th.img.susercontent.com/sg-11134201-81zv9-miz9ow3oi8lj42.webp</t>
@@ -7345,7 +6450,6 @@
           <t>https://s.shopee.co.th/60P0xz4s5m</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mm9pizydk5xc4b.webp</t>
@@ -7371,7 +6475,6 @@
           <t>https://s.shopee.co.th/9fIMqLzOpO</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mgyx989f9wjyee.webp</t>
@@ -7397,7 +6500,6 @@
           <t>https://s.shopee.co.th/AKY3da5f1i</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0n-md9qzjt7ct6te4.webp</t>
@@ -7423,7 +6525,6 @@
           <t>https://s.shopee.co.th/6pyBT9emG1</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mf9cwj4meo7j8e.webp</t>
@@ -7449,7 +6550,6 @@
           <t>https://s.shopee.co.th/8fPpeXH6LG</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-820l6-mny26tk8marpe2.webp</t>
@@ -7475,7 +6575,6 @@
           <t>https://s.shopee.co.th/6AiUfwh7Li</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mm9pizydk5xc4b.webp</t>
@@ -7501,7 +6600,6 @@
           <t>https://s.shopee.co.th/6felGsaCig</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-mowa2md7wv0ua6.webp</t>
@@ -7527,7 +6625,6 @@
           <t>https://s.shopee.co.th/70HbfUnRNJ</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mgyqwnqefmz20f.webp</t>
@@ -7553,7 +6650,6 @@
           <t>https://s.shopee.co.th/2g8cVYCKiP</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-lqiuhgx3ja5x71.webp</t>
@@ -7579,7 +6675,6 @@
           <t>https://s.shopee.co.th/LkhjHADzm</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r98w-lr32ynz35a3y01.webp</t>
@@ -7605,7 +6700,6 @@
           <t>https://s.shopee.co.th/4LGqUdqfsz</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mmerdhr96n7pa2.webp</t>
@@ -7631,7 +6725,6 @@
           <t>https://s.shopee.co.th/5q5eHP3Wdx</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7r992-ln2pq63i6vmbe6.webp</t>
@@ -7657,7 +6750,6 @@
           <t>https://s.shopee.co.th/2LVm6z2d0b</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasg-m26exktsvcmc99.webp</t>
@@ -7683,7 +6775,6 @@
           <t>https://s.shopee.co.th/3qKZtkVMKT</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mnr8p5khut5285.webp</t>
@@ -7709,7 +6800,6 @@
           <t>https://s.shopee.co.th/902g3FTHyJ</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-82609-mkizr73xsbuw07.webp</t>
@@ -7735,7 +6825,6 @@
           <t>https://s.shopee.co.th/3B4t6Y32zr</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mowk6nj69zwgd4.webp</t>
@@ -7761,7 +6850,6 @@
           <t>https://s.shopee.co.th/2BCLuiapM1</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-miv8q6eknabnf9.webp</t>
@@ -7787,7 +6875,6 @@
           <t>https://s.shopee.co.th/2VpCJLmDSa</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-7req2-m8pxgngdv40l86.webp</t>
@@ -7813,7 +6900,6 @@
           <t>https://s.shopee.co.th/70Hbfe0ANc</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-825ad-mfw72a2atxceb0.webp</t>
@@ -7839,7 +6925,6 @@
           <t>https://s.shopee.co.th/9zvDFAt157</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasa-m8d3k7f7lwq6f3.webp</t>
@@ -7865,7 +6950,6 @@
           <t>https://s.shopee.co.th/60P4TpgY32</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-81zte-minvdih1cu0yc9.webp</t>
@@ -7891,7 +6975,6 @@
           <t>https://s.shopee.co.th/4ftgtOGhHU</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mifmrl2yr2mac9.webp</t>
@@ -7917,7 +7000,6 @@
           <t>https://s.shopee.co.th/20sviV4n31</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-miva3n0wouf766.webp</t>
@@ -7943,7 +7025,6 @@
           <t>https://s.shopee.co.th/4ftgtPBcPD</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-mmze5hm4pfr8b5.webp</t>
@@ -7969,7 +7050,6 @@
           <t>https://s.shopee.co.th/BRHX93s8c</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/sg-11134201-823ph-moji0krg90qq78.webp</t>
@@ -7995,7 +7075,6 @@
           <t>https://s.shopee.co.th/W47vlItbl</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mp0hbammrpjha9.webp</t>
@@ -8021,7 +7100,6 @@
           <t>https://s.shopee.co.th/70Hbfig4Bv</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7ra0m-mchn1vs61k3k96.webp</t>
@@ -8047,7 +7125,6 @@
           <t>https://s.shopee.co.th/AAEdRXyoFE</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztd-mopi2qw2tpfz5e.webp</t>
@@ -8073,7 +7150,6 @@
           <t>https://s.shopee.co.th/6VLL4p7pKh</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m3w2qlqdirfr06.webp</t>
@@ -8099,7 +7175,6 @@
           <t>https://s.shopee.co.th/W47vnvCj5</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/cn-11134207-7r98o-ln5f8rpzzj4td3.webp</t>
@@ -8125,7 +7200,6 @@
           <t>https://s.shopee.co.th/6AiUgDiucz</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81ztl-megyhegt7lza86.webp</t>
@@ -8151,7 +7225,6 @@
           <t>https://s.shopee.co.th/9pbn2xnrJV</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mn5dwz9pd3i8a5.webp</t>
@@ -8180,7 +7253,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["F", "A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 13448 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇"]}</t>
+          <t>{"last_personas": ["A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1"], "recent_captions": ["ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5030,6 +5030,11 @@
           <t>฿187</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>done 2026-07-25 19:45</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -7253,7 +7258,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["A", "B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ"], "last_styles": ["มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ"], "last_roles": ["R8", "R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1"], "recent_captions": ["ไม่คิดว่าจะ... ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ New Hisense TV นิ้ว ราคาแค่ 15590 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68"]}</t>
+          <t>{"last_personas": ["B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5060,6 +5060,11 @@
           <t>฿179</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>done 2026-07-26 19:43</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -7258,7 +7263,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E"], "last_hooks": ["เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ..."], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)"], "last_roles": ["R4", "R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4"], "recent_captions": ["เมื่อวานเพิ่งเจอ... แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ครื่องบดหมู บดมันหมู กระเทียม บดหยาบ ราคาแค่ 3689 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187"]}</t>
+          <t>{"last_personas": ["H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5090,6 +5090,11 @@
           <t>฿225</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>done 2026-07-27 20:57</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -7263,7 +7268,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["H", "C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B"], "last_hooks": ["ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ..."], "last_styles": ["คำถาม", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)"], "last_roles": ["R7", "R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8"], "recent_captions": ["ตอนแรกไม่ได้จะซื้อ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น แอร์เคลื่อนที่ All-in-one ./ แอร์ขนาดเล็ก ราคาแค่ 4989 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
+          <t>{"last_personas": ["C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5120,6 +5120,11 @@
           <t>฿48</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>done 2026-07-28 20:17</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7268,7 +7273,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F"], "last_hooks": ["แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก"], "last_roles": ["R7", "R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7"], "recent_captions": ["แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Hisense ทีวี นิ้ว Full ราคาแค่ 5418 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225"]}</t>
+          <t>{"last_personas": ["B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5150,6 +5150,11 @@
           <t>฿87</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>done 2026-07-29 20:22</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -7273,7 +7278,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["B", "C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D"], "last_hooks": ["กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่"], "last_styles": ["คำถาม", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R6", "R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2"], "recent_captions": ["กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น IMARFLEX หม้อนึ่งไฟฟ้า เครื่องนึ่งไอน้ำอเนกปร ราคาแค่ 1090 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48"]}</t>
+          <t>{"last_personas": ["C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H"], "last_hooks": ["โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม"], "last_roles": ["R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5180,6 +5180,11 @@
           <t>฿330</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>done 2026-07-30 20:13</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -7278,7 +7283,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H"], "last_hooks": ["โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี"], "last_styles": ["การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม"], "last_roles": ["R1", "R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4"], "recent_captions": ["โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Presale พร้อมส่ง มิย Hisense ราคาแค่ 10390 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87"]}</t>
+          <t>{"last_personas": ["G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก"], "last_roles": ["R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5210,6 +5210,11 @@
           <t>฿192</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>done 2026-07-31 20:18</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -7283,7 +7288,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B"], "last_hooks": ["มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที"], "last_styles": ["การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก"], "last_roles": ["R4", "R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2"], "recent_captions": ["มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ ของกิน ดีๆครับ ตัวนี้มีจุดเด่นคือ xBloom เครื่องชงกาแฟอัตโนมัติ รุ่น Studio ราคาแค่ 26877 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330"]}</t>
+          <t>{"last_personas": ["G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5240,6 +5240,11 @@
           <t>฿56</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>done 2026-08-02 19:41</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -7288,7 +7293,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["G", "C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F"], "last_hooks": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม"], "last_styles": ["ประสบการณ์ส่วนตัว (PAS)", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)"], "last_roles": ["R7", "R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5"], "recent_captions": ["ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ลองซื้อ แก้วเก็บความเย็น ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง SMARTHOME เตาแม่เหล็กไฟฟ้า พร้อมหม้อและฝาแก้ว ราคาแค่ 519 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192"]}</t>
+          <t>{"last_personas": ["C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5", "R8"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿56"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5270,6 +5270,11 @@
           <t>฿179</t>
         </is>
       </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>done 2026-08-03 21:00</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -7293,7 +7298,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["C", "D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F", "E"], "last_hooks": ["เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี"], "last_styles": ["การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก"], "last_roles": ["R7", "R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5", "R8"], "recent_captions": ["เห็นคนพูดถึงเยอะเลยลอง ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ประกัน3ปี SKYWORTH นิ้ว Google ราคาแค่ 11490 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿56"]}</t>
+          <t>{"last_personas": ["D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F", "E", "B"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม"], "last_roles": ["R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5", "R8", "R8"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿56", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -5300,6 +5300,11 @@
           <t>฿159</t>
         </is>
       </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>done 2026-08-04 20:21</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -7298,7 +7303,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{"last_personas": ["D", "E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F", "E", "B"], "last_hooks": ["อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง"], "last_styles": ["การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม"], "last_roles": ["R8", "R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5", "R8", "R8"], "recent_captions": ["อันนี้เกินคาดจริงๆ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น Masterkoolเครื่องฟอกอากาศPM2.5และUVCฆ่าเชื้อไ ราคาแค่ 6390 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿56", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179"]}</t>
+          <t>{"last_personas": ["E", "C", "C", "G", "E", "A", "E", "A", "E", "E", "D", "D", "C", "B", "E", "E", "H", "D", "G", "D", "H", "F", "C", "D", "A", "G", "G", "A", "F", "E", "C", "F", "H", "B", "G", "E", "B", "C", "C", "B", "E", "B", "F", "D", "H", "B", "F", "E", "B", "B"], "last_hooks": ["ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ", "ไม่คิดว่าจะ...", "เมื่อวานเพิ่งเจอ...", "ตอนแรกไม่ได้จะซื้อ", "แชร์เผื่อมีคนกำลังหาอยู่", "กำลังหาของแบบนี้อยู่พอดี", "โดนป้ายยามาอีกที", "มีใครเป็นเหมือนผมไหม", "ลองแล้วเข้าใจเลยว่าทำไมขายดี", "เห็นคนพูดถึงเยอะเลยลอง", "อันนี้เกินคาดจริงๆ"], "last_styles": ["ประสบการณ์ส่วนตัว", "มุกตลก", "การบอกต่อเฉยๆ", "ประสบการณ์ส่วนตัว", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "คำถาม", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "คำถาม", "การเปรียบเทียบ (BAB)", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การบอกต่อเฉยๆ", "คำถาม", "มุกตลก", "มุกตลก", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "มุกตลก", "การเปรียบเทียบ", "ประสบการณ์ส่วนตัว", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "คำถาม", "คำถาม", "ประสบการณ์ส่วนตัว", "คำถาม", "การเปรียบเทียบ", "การบอกต่อเฉยๆ", "การบอกต่อเฉยๆ", "การเปรียบเทียบ (BAB)", "การเปรียบเทียบ (BAB)", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "คำถาม", "มุกตลก", "ประสบการณ์ส่วนตัว (PAS)", "มุกตลก", "คำถาม", "มุกตลก"], "last_roles": ["R6", "R7", "R4", "R2", "R3", "R8", "R4", "R6", "R2", "R5", "R5", "R8", "R4", "R1", "R4", "R4", "R1", "R2", "R3", "R7", "R5", "R4", "R5", "R1", "R6", "R8", "R8", "R1", "R6", "R7", "R6", "R5", "R1", "R7", "R2", "R1", "R1", "R5", "R4", "R1", "R4", "R8", "R7", "R2", "R4", "R2", "R5", "R8", "R8", "R4"], "recent_captions": ["ไม่คิดว่าจะ... หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง New TCL BreezeIN แอร์ ราคาแค่ 24524 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สินค้าตัวนี้เลยครับ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive ตู้เย็นหน้ากระจก มินิบาร์ ราคาแค่ 4690 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ สินค้าใหม่ SMARTHOME หม้อทอดไร้น้ำมันขนาด . ราคาแค่ 1118 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง Smarthome เครื่องกรองอากาศ กรองและบอกระดับ รุ ราคาแค่ 1776 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ TCL ตู้เย็น Side by ราคาแค่ 21892 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ราคาแค่ 143 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น SHARP เครื่องฟอกอากาศ รุ่น FP-/B ราคาแค่ 4190 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ 💕คุณภาพระดับสูง💕ICE Cream Machine ประหยัดไฟ ราคาแค่ 25487 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ เทียบกับ ของใช้สัตว์เลี้ยง แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น LG เครื่องซักผ้า กิโล รุ่นTT14NARG.DBMPETH ราคาแค่ 6890 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 44090 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ลองซื้อ ทีวี ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ABL LED TV \" ราคาแค่ 4299 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง HAIER เครื่องปรับอากาศ รุ่น HSU-VQAC ราคาแค่ 11871 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ พกไปกินตอนบ่ายที่ออฟฟิศอิ่มท้องกำลังดี ไม่ต้องเดินไปกดน้ำหวาน เทียบกับ นมโปรตีน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น TOSHIBA ตู้เย็นมินิบาร์ ความจุ . ราคาแค่ 4408 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง ของกิน ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น เก็บปลายทางAOYANG Smart MPPT Solar ราคาแค่ 2970 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น FOTILE เครื่องดูดควันกระโจม ซม. + ราคาแค่ 34900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง KAWU หม้อต้มไฟฟ้า เดือดทันที การควบคุมอุณหภูม ราคาแค่ 799 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม สินค้าตัวนี้เลยครับ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Online Exclusive Tefal เตารีดแรงดันไอน้ำ ราคาแค่ 3270 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ SAMSUNG นิ้ว OLED Tizen ราคาแค่ 63490 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง ช่วงควบคุมอาหาร ดูแลหุ่นอยู่ ได้ตัวนี้ช่วยชีวิตไว้เลย แคลน้อยโปรตีนสูง เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW TCL ทีวี นิ้ว ราคาแค่ 75990 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ในฐานะแม่บ้านที่ชอบหาของเข้าครัว ดูแลคนในบ้าน แนะนำเลยค่ะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ LJP / / 70Lพัดลมไอเย็น ราคาแค่ 1699 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะ... คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก มีใครเคยลอง ทีวี ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น Hisense ทีวี รุ่น ขนาด ราคาแค่ 20679 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอ... ทีวีตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Hisense TV นิ้ว รุ่น ราคาแค่ 26355 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ ทีวีตัวนี้เลยครับ คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 30790 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น iFFALCON iECO Series ขนาด ราคาแค่ 9355 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น แถมฟรี! ตู้เย็น รุ่น Hisense ราคาแค่ 14372 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล เทียบกับ ของกิน แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น เครื่องบดอเนกประสงค์ เครื่องบดแป้ง เครื่องบด  ราคาแค่ 4488 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ทีวีตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Toshiba TV ทีวี นิ้ว ราคาแค่ 11040 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก เทียบกับ ทีวี แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น NEW SHARP TV นิ้ว ราคาแค่ 16900 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง สินค้าตัวนี้เลยครับ หลังเวทเสร็จเหนื่อยๆ ขี้เกียจเคี้ยวอกไก่ ได้ตัวนี้ดื่มทดแทนสะดวกมาก ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ Tuya Video HD ไร้สายกันน้ําออดกล้องรีโมทคอนโท ราคาแค่ 869 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ เมื่อก่อนผมปวดหัวกับทีวีเครื่องเก่าที่เล่นเกมทีไรก็ภาพกระตุก แถมเสียงแบนๆ ลำโพงแห้งมาก แต่พอเปลี่ยนมาใช้ทีวี MiniLED รุ่น Q7D ขนาด 65-75 นิ้ว ราคา 35590 ตัวนี้แล้วคนละเรื่องเลยครับ เพราะได้จอ 144Hz VRR ที่ลื่นไหลสมจริงต่างจากเดิมเยอะ บวกกับลำโพง Onkyo เสียงกระหึ่มมีมิติโดยไม่ต้องต่อลำโพงแยกให้วุ่นวายอีกต่อไป ใครกำลังหาทีวีเล่นเกมเครื่องใหม่เซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ไม่คิดว่าจะเจอเครื่องดูดฝุ่นถูพื้นรุ่น CrossWave Pet Pro ลดราคาลงมาเหลือ 17599 บาทแบบบังเอิญขนาดนี้ หลังจากที่ผมเอามาลองใช้ทำความสะอาดบ้านจริง ตัวนี้เด่นตรงที่เป็นแบบ 3in1 ดูด ล้าง เช็ดแห้ง จบในเครื่องเดียว ช่วยประหยัดเวลาชีวิตไปเยอะมากครับ ใครที่ปวดหัวกับงานบ้านบ่อยๆ แชร์ต่อให้เพื่อนหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เมื่อวานเพิ่งเจอทางสว่างหลังจากที่ปกติผมกวาดบ้านทีไรฝุ่นตลบจนไอคอกแคก แฟนเกือบจะโทรเรียกกู้ภัยนึกว่าผมใกล้สิ้นอายุขัยแล้วครับ พอได้ลองเปลี่ยนมาใช้ เครื่องดูดฝุ่นไร้สาย ตัวนี้ที่แรงดูดสูง 99000Pa แถมชาร์จ USB ได้ ชีวิตหลังใช้ดีขึ้นเยอะ ฝุ่นไม่เกาะหน้าจนหน้าเทาเหมือนเมื่อก่อน ในราคาแค่ 199 บาท มีรับประกัน 1 ปีด้วย ใครที่ขี้เกียจกวาดบ้านจนห้องรกเหมือนผม เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ตอนแรกไม่ได้จะซื้อ แต่ผมอยากหา แบตเจลโซล่าเซลล์ รุ่น NPP ขนาด 12V 55Ah ไปช่วยสำรองไฟที่บ้านให้พ่อแม่รู้สึกอุ่นใจขึ้นครับ ตัวนี้เป็นแบบ Deep Cycle มีรับประกันให้พร้อม ในราคา 2499 บาท สมาชิกในบ้านแฮปปี้มาก ใครแพลนจะทำไฟบ้านเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้ครอบครัวดูได้เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "แชร์เผื่อมีคนกำลังหาอยู่ มีใครกำลังเจอปัญหาภูมิแพ้เล่นงานจนนอนไม่ค่อยสบายเหมือนผมบ้างไหมครับ? ผมลองใช้เครื่องฟอกอากาศ รุ่น X8proUltra (D) ที่เหมาะกับขนาดห้อง 60-120 ตร.ม. มาระยะหนึ่ง รู้สึกได้เลยว่าอากาศในบ้านสะอาดขึ้นเยอะเพราะตัวนี้ช่วยกรองฝุ่น PM 2.5 และฆ่าเชื้อไวรัสได้ด้วย ถึงราคาจะอยู่ที่ 60900 บาท แต่เพื่อสุขภาพของครอบครัวผมว่าเป็นการลงทุนที่ตอบโจทย์ครับ ใครที่กำลังมีปัญหาเรื่องอากาศในบ้าน ลองเซฟเก็บไว้ดูตอนช้อป หรือจะแชร์ต่อให้เพื่อนที่เจอปัญหานี้อยู่ก็ได้นะครับ \n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "กำลังหาของแบบนี้อยู่พอดี สายของอร่อยอย่างเราลองแล้วดื่มด่ำมาก ฟินสุดๆ มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น พัดลมติดผนัง หมุนเวียนอากาศ ไม่ต้องเจาะรู สํา ราคาแค่ 997 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "โดนป้ายยามาอีกที ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก ลองซื้อ สินค้า ตัวนี้มาใช้ได้สักพักแล้วครับ รู้สึกสะดวกสบายขึ้นเยอะ โดยเฉพาะเรื่อง ปลั๊กพ่วง ปลั๊กสนาม บล็อกยาง สาย ราคาแค่ 109 บาท ดีจริง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "มีใครเป็นเหมือนผมไหม ในฐานะพ่อบ้านที่ชอบจัดบ้านดูแลงานบ้าน บอกเลยว่าถูกใจมาก มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น HAIER แอร์ ขนาด , ราคาแค่ 12712 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "ลองแล้วเข้าใจเลยว่าทำไมขายดี คนรักสัตว์อย่างเราหาของดีๆ มาให้เด็กๆ ตลอด ตัวนี้ตอบโจทย์มาก เทียบกับ สินค้า แบบเดิมๆ ที่เคยใช้ ตัวนี้คือจุดเด่น ปลั๊กไฟ ช่อง W ปลั๊กพ่วง ราคาแค่ 64 บาท ดีกว่าเห็นๆ เลยครับ\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "เห็นคนพูดถึงเยอะเลยลอง แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ แวะมาแชร์ สินค้า ดีๆครับ ตัวนี้มีจุดเด่นคือ ทักแชทก่อนสั่งซื้อ.6โปรx6🔥รับส่วนลด300บาทx7เด ราคาแค่ 199 บาท เผื่อใครกำลังสนใจอยู่\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇", "อันนี้เกินคาดจริงๆ ผมกดสั่งพัดลมพกพารุ่น Turbo มาลองใช้สักพักแล้ว ปรับลมได้ตั้ง 100 ระดับ แถมมีจอดิจิทัลบอกตัวเลขชัดเจนมาก ตัวนี้ได้มาในราคา 68 บาทเองครับ ใครกำลังหาพัดลมมินิไว้คลายร้อน กดเซฟโพสต์นี้เก็บไว้ หรือแชร์ต่อให้เพื่อนที่กลัวร้อนได้เลย ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿68", "ไม่คิดว่าจะต้องทนอึดอัดกับการใส่ยีนส์ผ้าแข็งๆ แน่นพุงทุกครั้งที่นั่งทำงานจนไม่อยากแต่งตัวเลยครับ แต่พอเปลี่ยนมาใส่กางเกงยีนส์เอวยืดทรงหลวม รุ่น MNO.9 5080 ราคา 187 บาท ชีวิตผมดีขึ้นเยอะ นั่งสบายไม่รัดพุง แถมมีเชือกรูดปรับระดับได้ตามใจชอบครับ กางเกงยีนส์ตัวนี้เปลี่ยนวันอึดอัดให้กลายเป็นใส่ชิลๆ ได้ทุกวัน แชร์ต่อให้เพื่อนสายกินหรือเซฟเก็บไว้ดูได้นะครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿187", "เมื่อวานเพิ่งเจอรูปเก่าๆ ตอนที่ผมต้องนั่งทนหนาวทำงานเพราะใส่แค่เสื้อบางๆ แต่ตอนนี้สบายขึ้นเยอะ พอได้ลองใส่เสื้อฮู้ด รุ่น M248 ผ้าสำลีหนานุ่ม คอยให้ความอบอุ่น แถมมีกระเป๋าหน้าไว้ซุกมือ เสื้อกันหนาวตัวนี้ในราคา 179 บาท ช่วยให้ชีวิตช่วงอากาศเย็นของผมเปลี่ยนไปเลย เซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนที่เจอปัญหานี้ได้เลยครับ\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "ตอนแรกไม่ได้จะซื้อ แต่พอมองกระจกเห็นทรงผมหัวฟูเหมือนโดนฟ้าผ่าของตัวเองแล้ว มือมันเผลอกดสั่งไดร์จัดแต่งทรงผม รุ่น 6268/PAE3012 แบบคละสีมาจนได้ครับ ยิ่งเห็นเขามีโปรลูกค้าใหม่ 1 บาท จากราคาปกติ 225 บาท ยิ่งต้องรีบกดเลย ใครอยากได้ตัวช่วยเซตผมกดเซฟเก็บไว้ดูตอนช้อป หรือแชร์ต่อให้เพื่อนที่ทรงผมสภาพเดียวกับผมดูครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿225", "แชร์เผื่อมีคนกำลังหาอยู่ เมื่อก่อนห้องผมรกมาก ของวางเกะกะไปหมด จะหยิบอะไรทีต้องเสียเวลานั่งรื้อจนหงุดหงิดทุกวัน พอได้กล่องเก็บของตัวนี้มาช่วยจัดระเบียบบ้านก็ง่ายขึ้นเยอะ เพราะตัวกล่องโปร่งใสทำให้มองเห็นของข้างในได้ทันที แถมมีความจุสูง ใส่ของได้เยอะมากในราคา 48 บาทครับ ใครเจอปัญหาเดียวกัน เซฟเก็บไว้ดูหรือแชร์ต่อให้เพื่อนได้เลยนะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿48", "\"กำลังหาของแบบนี้อยู่พอดี\" มีใครกำลังมองหาหูฟังไร้สายเอาไว้แบ่งให้คนในบ้านใช้ฟังเพลงกันบ้างไหมครับ? พอดีผมไปเจอหูฟังรุ่น TWS มาพร้อมกล่องชาร์จ ในราคา 87 บาท แถมยังมีโปรซื้อ 1 แถม 1 ได้มาคู่กันเลยครับ ลองเซฟเก็บไว้ดูตอนช้อป หรือแชร์โพสต์นี้ให้คนที่บ้านดูก่อนได้นะครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿87", "โดนป้ายยามาอีกที เห็นเขาฮิตกิน ผงอาซาอิ บำรุงผิว กัน ผมก็นึกว่าจะช่วยเปลี่ยนหน้าโทรมๆ ของผมเป็นดาราเกาหลีได้ เลยลองกดแบบฟรีซดราย ขนาด 80g ในราคา 330 บาท มาลองกินมาระยะนึงแล้วครับ สรุปหน้ายังเป็นผมคนเดิม แต่ก็ได้ลองกินผงอาซาอิฟรีซดรายตามกระแสสมใจ ใครชอบลองเซฟเก็บไว้ดูตอนช้อปหรือแชร์ต่อให้เพื่อนได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿330", "มีใครเป็นเหมือนผมไหม เวลาออกไปข้างนอกทีไร มือไม้เหมือนมีพลังดึงดูดเชื้อโรคจับโน่นจับนี่แล้วเผลอเอามาถูหน้าตัวเองตลอดครับ อึดอัดนอยด์ไปหมดจนกลัวเชื้อโรคจะเดินตามเข้าบ้านไปด้วย แต่พอมีทิชชู่เปียกฆ่าเชื้อ รุ่น CC-DL0980 ห่อสีฟ้า เกรดโรงพยาบาล IPA 70% ขนาด 80 แผ่น ราคา 192 บาท มาช่วยเช็ดทำความสะอาดรอบตัวก็สบายใจขึ้นเยอะ แชร์ต่อให้เพื่อนสายระแวงหรือเซฟเก็บไว้ดูตอนช้อปได้เลยครับ ดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿192", "ลองแล้วเข้าใจเลยว่าทำไมขายดี สินค้าตัวนี้เลยครับ สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ รับประกัน ปี TWS หูฟังบลูทูธไร้สาย ราคาแค่ 56 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿56", "เห็นคนพูดถึงเยอะเลยลอง สายช้อปของคุ้มหารเฉลี่ยราคาต่อชิ้นแล้วประหยัดมาก คุ้มค่าน้ำตาไหล มีใครเคยลอง สินค้า ตัวนี้รึยังครับ ส่วนตัวประทับใจจุดเด่น 🫘ธัญพืชรวม เซียน กรัม ไม่ใส่เนย ราคาแค่ 179 บาท คิดว่าไงกันบ้าง\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿179", "อันนี้เกินคาดจริงๆ สินค้าตัวนี้เลยครับ แช่ตู้เย็นที่ออฟฟิศไว้ เวลาหิวดึกหิวยามบ่ายช่วยชีวิตพนักงานออฟฟิศได้เยอะ ตอนแรกกังวลว่าจะไม่โอเค แต่พอลองแล้วชอบเลย รอดตายแล้วเรา 555 จุดเด่นคือ ⚡ ลูกค้าใหม่ บาท! พัดลมมือถือเทอร์โบ ราคาแค่ 159 บาท\n\nดูลิ้งในคอมเมนต์แรกเลยครับ 👇\n🔥 โปรโมชั่น: ฿159"]}</t>
         </is>
       </c>
     </row>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -486,12 +486,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ของเล่นโมเดลรถถังทหาร เครื่องบินทหาร สำหรับเด็ก ของเล่นบล็อคตัวต่อฝึกเสริมสมาธิ</t>
+          <t>MEIYIJIA เครื่องดูดฝุ่นในรถ ไร้สาย 12000Pa car vacuum cleaner เครื่องดูดฝุ่นขนาดเล็ก ที่ดูดฝุ่นในรถยนต์ ภายในบ้าน เตียง</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/20uOne6kLC</t>
+          <t>https://s.shopee.co.th/7Kvv9iFNqe</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
@@ -505,12 +505,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>สินค้าใหม่ 2026 scale 1:72 โมเดลประกอบ บล็อก ตัวต่อ รถทหาร รถถัง T90 T14 M1A2 เครื่องบิน</t>
+          <t>แบตเตอรี่ 12V 8AH/12AH UPS ไฟฉุกเฉิน เครื่องมือเกษตร ใส่เครื่องพ่นยา สินค้าพร้อมส่งในไทย</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAG6Wfo2Uy</t>
+          <t>https://s.shopee.co.th/9pdG8KMRW0</t>
         </is>
       </c>
       <c r="D3" s="2" t="n"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>โมเดลรถถังอาวุธทหาร UK US WW2 ของเล่นสําหรับเด็ก ของขวัญวันเกิด 524 ชิ้น Sluban 0858</t>
+          <t>แบตเตอรี่12V 20Ah แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VqfObCYkg</t>
+          <t>https://s.shopee.co.th/8fRIkCQTpy</t>
         </is>
       </c>
       <c r="D4" s="2" t="n"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ProudNada Toys ตัวต่อ ทหาร รถถัง รถหุ้มเกราะ SLUBAN MODEL BRICKS M4A3(76W) MEDIUM TANK 715 PCS M38-B1110</t>
+          <t>แบตเตอรี่ลิเธียม 12V 10AH/22AH แบตเตอรี่ สามารถชาร์จโดยใช้พลังงานแสงอาทิตย์แล แบตเตอรี่เครื่องพ่นสารเคมี แบตเตอรี</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5q77Mkho5s</t>
+          <t>https://s.shopee.co.th/70J4l9fhZH</t>
         </is>
       </c>
       <c r="D5" s="2" t="n"/>
@@ -562,12 +562,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>M2 Bradley รถหุ้มเกราะทหารราบ เข้ากันได้ตัวต่อเลโก้ 1862ชิ้น 12GO Tank โมเดลประกอบแล้ว</t>
+          <t>แบตเตอรี่12V 20Ah แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1Vy8CoShJr</t>
+          <t>https://s.shopee.co.th/8pkiwXqoKq</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CH-53E เฮลิคอปเตอร์ทหาร เข้ากันได้ตัวต่อเลโก้ 2192ชิ้น Reobrix Plane โมเดลประกอบแล้ว</t>
+          <t>เครื่องดูดฝุ่นในรถยนต์ เครื่องดูดฝุ่นไร้สาย แรงดูดสูง 99000Pa เครื่องดูดฝุ่นพกพา ชาร์จUSB ส่งด่วนจากไทย</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BDp03Gt5Y</t>
+          <t>https://s.shopee.co.th/7Kvv9o8M0p</t>
         </is>
       </c>
       <c r="D7" s="2" t="n"/>
@@ -600,12 +600,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>สินค้าใหม่ปี 2026 โมเดลเครื่องบิน เฮลิคอปเตอร์ f35 f16 j10 f14 รถทหาร ทหาร</t>
+          <t>เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิทธิภาพพายุไซโคลนดูดแบบพกพาชาร์จเครื่องดูดฝุ่น ไร้สาย ที่ดูดฝุ่น ดูดฝุ่นในรถ</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJpvqwjNy</t>
+          <t>https://s.shopee.co.th/5LAqm9OQqo</t>
         </is>
       </c>
       <c r="D8" s="2" t="n"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ProudNada Toys ของเล่นเด็ก ตัวต่อ เฮลิคอปเตอร์ ทหาร Sluban Model Bricks KA-50 330 PCS B0752</t>
+          <t>ที่ใส่ก้านกันสาด ฐานเสาดัก Tarp Pole Fixator มีน็อตคู่ แบบปรับได้ หลากสีอุปกรณ์เสริม สําหรับตั้งเต็นท์</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/qiRPdUIZW</t>
+          <t>https://s.shopee.co.th/8pkiwbFNXY</t>
         </is>
       </c>
       <c r="D9" s="2" t="n"/>
@@ -638,12 +638,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>โมเดลกระดาษประกอบเครื่องบินขนส่งทหาร AC-130U Spooky Gunship - MohinhgiayVN</t>
+          <t>ตัวล็อคฮุคแขวนสินค้า ระบบแม่เหล็ก สีแดง ขนาด 4 5 6 7 8 mm สำหรับร้านค้า ร้านไอที</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5VUGyE2MpD</t>
+          <t>https://s.shopee.co.th/2VqfOyh4Z1</t>
         </is>
       </c>
       <c r="D10" s="2" t="n"/>
@@ -657,12 +657,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MOC Assembly Toy Army ZU-23-2 โมเดลทหาร</t>
+          <t>BONMECOM2 / ปลั๊กไฟ Melon/ ปลั๊กไฟโต๊ะคอม/ ปลั๊กไฟโต๊ะทำงาน 2 ช่อง 1 สวิตซ์ 3USB (1.5M) มี มอก. (ของแถมคละสี)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJpvts59O</t>
+          <t>https://s.shopee.co.th/3qM2zRT4Ho</t>
         </is>
       </c>
       <c r="D11" s="2" t="n"/>
@@ -676,12 +676,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MOC Assembly Toy Army LAV-25 โมเดลทหาร</t>
+          <t>ปลั๊กไฟ 3 4 5 ช่อง 2300 W ปลั๊กพ่วง สายยาว 3 เมตร 5 เมตร8 เมตร</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2BDp08NfRA</t>
+          <t>https://s.shopee.co.th/2VqfP0SeYX</t>
         </is>
       </c>
       <c r="D12" s="2" t="n"/>
@@ -695,12 +695,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MOC Assembly Toy Army ZSU-234 โมเดลทหาร</t>
+          <t>ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม 2x4 บล็อกยาง สาย VCT2x1 รองรับไฟสูงสุด 3000W ยาว 5M,10M,15M,20M,30M</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6L3Nxnyo90</t>
+          <t>https://s.shopee.co.th/5LAqmFdXSe</t>
         </is>
       </c>
       <c r="D13" s="2" t="n"/>
@@ -714,12 +714,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>บล็อกตัวต่อโมเดลฟิกเกอร์ รูปเมืองทหาร ยาว 1x16 Diy ของเล่นสร้างสรรค์ ของขวัญ 5 ชิ้น</t>
+          <t>ปลั๊กไฟ 3/5 รู, หลายเต้ารับ, แถบสายไฟต่อ, ปลั๊กสายไฟต่อ, แจ็คชาร์จไฟ USB, รางปลั๊กไฟ, สายยาว 2/3/5M เมตร</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaybYARpE</t>
+          <t>https://s.shopee.co.th/4fv9z2cEeM</t>
         </is>
       </c>
       <c r="D14" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>4D MODEL โมเดลหุ่นทหารมินิ หุ่นจำลอง สินค้าแท้ ลิขสิทธิ์ถูกต้อง Miniature assembly special Troops Army Figures MMXJ-98</t>
+          <t>ปลั๊กพ่วง ปลั๊กสนาม 2x4 บล็อกยาง สาย VCT 24sq.mm รองรับไฟสูงสุด 3000W ยาว 5M,10M,15M,20M หุ้มยางต่อสายไฟ สายไฟหุ้มฉนวน</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5ArQZgxlab</t>
+          <t>https://s.shopee.co.th/7VFLMGHDMA</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -752,12 +752,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>โมเดลฟิกเกอร์ทหารทหารทหาร ขยับข้อต่อได้ ของเล่นสําหรับเด็กผู้ชาย</t>
+          <t>Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ปลั๊กสามตา ไฟ 10A 2500W ทนความร้อนได้ 750องศา Universal Adapter</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/60QXZFDEUS</t>
+          <t>https://s.shopee.co.th/3qM2zXPotA</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -771,12 +771,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MEIYIJIA เครื่องดูดฝุ่นในรถ ไร้สาย 12000Pa car vacuum cleaner เครื่องดูดฝุ่นขนาดเล็ก ที่ดูดฝุ่นในรถยนต์ ภายในบ้าน เตียง</t>
+          <t>ปลั๊กไฟพ่วงกลม 5 ช่อง 3 USB ความยาว 3 ,5, 8 เมตร</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kvv9iFNqe</t>
+          <t>https://s.shopee.co.th/7Kvv9z3MQv</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -790,12 +790,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>แบตเตอรี่ 12V 8AH/12AH UPS ไฟฉุกเฉิน เครื่องมือเกษตร ใส่เครื่องพ่นยา สินค้าพร้อมส่งในไทย</t>
+          <t>เก้าอี้แคมป์ปิ้ง พนักพิงสูง เก้าอี้สนาม พับได้ แบบพกพา ปิคนิค แถมถุงเก็บ รับน้ำหนัก 300KG</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9pdG8KMRW0</t>
+          <t>https://s.shopee.co.th/AAG6XCsmzJ</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>แบตเตอรี่12V 20Ah แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า</t>
+          <t>WTHB เก้าอี้แคมป์ปิ้ง เพิ่มผ้าฝ้าย พนักพิงสูง เก้าอี้สนาม เก้าอี้สนามพับได้ ปิคนิค รับน้ำหนัก 300KG</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8fRIkCQTpy</t>
+          <t>https://s.shopee.co.th/4fv9z7LZZT</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>แบตเตอรี่ลิเธียม 12V 10AH/22AH แบตเตอรี่ สามารถชาร์จโดยใช้พลังงานแสงอาทิตย์แล แบตเตอรี่เครื่องพ่นสารเคมี แบตเตอรี</t>
+          <t>ซื้อ 1 แถม1ไฟฉายคาดหัว ไฟคาดหัว ส่องไกล ไฟคาดหัว LED ส่องกบ เดินป่า ลุยฝนได้ สว่างมาก รับประกันความสว่า</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/70J4l9fhZH</t>
+          <t>https://s.shopee.co.th/1Vy8DJSgdv</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -847,12 +847,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>แบตเตอรี่12V 20Ah แบตเตอรี่แห้งแท้ รุ่น 6-DZF-20 แบตรถสามล้อไฟฟ้า รถจักรยานไฟฟ้า จักรยานไฟฟ้า,สกู๊ตเตอร์ สามล้อไฟฟ้า</t>
+          <t>20warehouse ไฟฉายคาดศีรษะ LED 90 Lumens ปรับมุมได้ ไฟส่องสว่างพกพา สำหรับเดินป่า กรีดยาง ซ่อมรถ ตกปลา</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pkiwXqoKq</t>
+          <t>https://s.shopee.co.th/40fTBvEz6Q</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>เครื่องดูดฝุ่นในรถยนต์ เครื่องดูดฝุ่นไร้สาย แรงดูดสูง 99000Pa เครื่องดูดฝุ่นพกพา ชาร์จUSB ส่งด่วนจากไทย</t>
+          <t>ซื้อ1แถม1ไฟฉายแรงสูง ไฟฉายLED ไฟฉายพกพา ชาร์จUSB ส่องสว่างไกล ปรับได้5ระดับ</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kvv9o8M0p</t>
+          <t>https://s.shopee.co.th/9fJpwLobn1</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -885,12 +885,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>เครื่องดูดฝุ่นมือถือ350วัตต์ไร้สายที่มีประสิทธิภาพพายุไซโคลนดูดแบบพกพาชาร์จเครื่องดูดฝุ่น ไร้สาย ที่ดูดฝุ่น ดูดฝุ่นในรถ</t>
+          <t>530 Portable Flashlights Miniไฟฉายสว่างมาก CREE LED XPE+COB 2in1 600mah usb charge 3mode ซูมได้</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LAqm9OQqo</t>
+          <t>https://s.shopee.co.th/2qTVno4nfp</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ที่ใส่ก้านกันสาด ฐานเสาดัก Tarp Pole Fixator มีน็อตคู่ แบบปรับได้ หลากสีอุปกรณ์เสริม สําหรับตั้งเต็นท์</t>
+          <t>เชือกรอกปรับระดับได้ เชือกเต็นท์ เชือกรอกปรับระดับได้ 4m สําหรับตั้งแคมป์กลางแจ้ง รอกเชือก เชือกยก</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/8pkiwbFNXY</t>
+          <t>https://s.shopee.co.th/1qaybz40f6</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -923,12 +923,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ตัวล็อคฮุคแขวนสินค้า ระบบแม่เหล็ก สีแดง ขนาด 4 5 6 7 8 mm สำหรับร้านค้า ร้านไอที</t>
+          <t>สมอบกเหล็กหล่อ สมอบกเต็นท์ วงแหวนเรืองแสง 20/30/40 CM เหล็กคาร์บอนสูง</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VqfOyh4Z1</t>
+          <t>https://s.shopee.co.th/5fnhB2pljE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BONMECOM2 / ปลั๊กไฟ Melon/ ปลั๊กไฟโต๊ะคอม/ ปลั๊กไฟโต๊ะทำงาน 2 ช่อง 1 สวิตซ์ 3USB (1.5M) มี มอก. (ของแถมคละสี)</t>
+          <t>มีดตั้งแคมป์กลางแจ้ง (สแตนเลส) - มีดอเนกประสงค์แบบพกพา คมชัดเป็นพิเศษ G3204</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qM2zRT4Ho</t>
+          <t>https://s.shopee.co.th/50Y0Npil9c</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ปลั๊กไฟ 3 4 5 ช่อง 2300 W ปลั๊กพ่วง สายยาว 3 เมตร 5 เมตร8 เมตร</t>
+          <t>#019 Kershaw #Folding knife #มีดพับ #มีดเดินป่า #มีดเอนกประสงค์ LIFEPLAZA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2VqfP0SeYX</t>
+          <t>https://s.shopee.co.th/2gA5bYimaj</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ปรับปรุงใหม่และเพิ่มความหนาขึ้นปลั๊กสนาม 2x4 บล็อกยาง สาย VCT2x1 รองรับไฟสูงสุด 3000W ยาว 5M,10M,15M,20M,30M</t>
+          <t>NANMEEBOOKS หนังสือ แผนที่ประวัติศาสตร์ เหตุการณ์เปลี่ยนโลก เสริมความรู้</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5LAqmFdXSe</t>
+          <t>https://s.shopee.co.th/6Ajxm0MsFI</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
@@ -999,12 +999,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ปลั๊กไฟ 3/5 รู, หลายเต้ารับ, แถบสายไฟต่อ, ปลั๊กสายไฟต่อ, แจ็คชาร์จไฟ USB, รางปลั๊กไฟ, สายยาว 2/3/5M เมตร</t>
+          <t>WAYFARER โต๊ะแคมป์กลางแจ้ง โต๊ะพับ โต๊ะไข่เจียว โต๊ะตั้งแคมป์ ซื้อ 1 แถม 1 ถุงจัดส่ง ง่ายต่อการพกพา ทำความสะอาดง่าย</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fv9z2cEeM</t>
+          <t>https://s.shopee.co.th/5fnhB6BArU</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ปลั๊กพ่วง ปลั๊กสนาม 2x4 บล็อกยาง สาย VCT 24sq.mm รองรับไฟสูงสุด 3000W ยาว 5M,10M,15M,20M หุ้มยางต่อสายไฟ สายไฟหุ้มฉนวน</t>
+          <t>MAX FIRE แก๊สกระป๋อง แก๊สปิคนิค พร้อมด้วยระบบป้องกันการระเบิด ปริมาณ 250g. ประเทศเกาหลี 1 แพ็ค</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7VFLMGHDMA</t>
+          <t>https://s.shopee.co.th/6Ajxm1pku2</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Deli ปลั๊กไฟ ปลั๊กแปลง ปลั๊กสากล ปลั๊กสามตา ไฟ 10A 2500W ทนความร้อนได้ 750องศา Universal Adapter</t>
+          <t>เชือกพาราคอร์ด เชือกตากผ้า เชือก ยาว4/10เมตร เก็บง่าย คุณภาพดี ทนทาน คละสี สำหรับเดินป่า ตั้งแคมป์ ใช้ผูกเอนกประสงค์</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3qM2zXPotA</t>
+          <t>https://s.shopee.co.th/AKZWjhSCbh</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ปลั๊กไฟพ่วงกลม 5 ช่อง 3 USB ความยาว 3 ,5, 8 เมตร</t>
+          <t>หมอนเป่าลม หมอนหนุนเป่าลมพกพา เบามาก จัดเก็บง่าย ขนาดพกพา 43x28x12cm หมอนเป่าลม ใบใหญ่ เหมาะสำหรับสำนักงาน การท่องเที่ยว</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/7Kvv9z3MQv</t>
+          <t>https://s.shopee.co.th/4qEaBblIDQ</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>เก้าอี้แคมป์ปิ้ง พนักพิงสูง เก้าอี้สนาม พับได้ แบบพกพา ปิคนิค แถมถุงเก็บ รับน้ำหนัก 300KG</t>
+          <t>ผ้าบัฟ ผ้าโพกหน้า ทั้งวิ่ง ล่าสัตว์ ตกปลา เดินป่า รถจักรยานยนต์ ปั่นจักรยาน เล่นสกี ชิคสุดๆค่าได้ยาวนานคุ้มค่า</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAG6XCsmzJ</t>
+          <t>https://s.shopee.co.th/3LPmOrdT84</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1088,293 +1088,8 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>WTHB เก้าอี้แคมป์ปิ้ง เพิ่มผ้าฝ้าย พนักพิงสูง เก้าอี้สนาม เก้าอี้สนามพับได้ ปิคนิค รับน้ำหนัก 300KG</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/4fv9z7LZZT</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>ซื้อ 1 แถม1ไฟฉายคาดหัว ไฟคาดหัว ส่องไกล ไฟคาดหัว LED ส่องกบ เดินป่า ลุยฝนได้ สว่างมาก รับประกันความสว่า</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/1Vy8DJSgdv</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>20warehouse ไฟฉายคาดศีรษะ LED 90 Lumens ปรับมุมได้ ไฟส่องสว่างพกพา สำหรับเดินป่า กรีดยาง ซ่อมรถ ตกปลา</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/40fTBvEz6Q</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>ซื้อ1แถม1ไฟฉายแรงสูง ไฟฉายLED ไฟฉายพกพา ชาร์จUSB ส่องสว่างไกล ปรับได้5ระดับ</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/9fJpwLobn1</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>530 Portable Flashlights Miniไฟฉายสว่างมาก CREE LED XPE+COB 2in1 600mah usb charge 3mode ซูมได้</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/2qTVno4nfp</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>เชือกรอกปรับระดับได้ เชือกเต็นท์ เชือกรอกปรับระดับได้ 4m สําหรับตั้งแคมป์กลางแจ้ง รอกเชือก เชือกยก</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/1qaybz40f6</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>สมอบกเหล็กหล่อ สมอบกเต็นท์ วงแหวนเรืองแสง 20/30/40 CM เหล็กคาร์บอนสูง</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/5fnhB2pljE</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>มีดตั้งแคมป์กลางแจ้ง (สแตนเลส) - มีดอเนกประสงค์แบบพกพา คมชัดเป็นพิเศษ G3204</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/50Y0Npil9c</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>#019 Kershaw #Folding knife #มีดพับ #มีดเดินป่า #มีดเอนกประสงค์ LIFEPLAZA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/2gA5bYimaj</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>NANMEEBOOKS หนังสือ แผนที่ประวัติศาสตร์ เหตุการณ์เปลี่ยนโลก เสริมความรู้</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/6Ajxm0MsFI</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>WAYFARER โต๊ะแคมป์กลางแจ้ง โต๊ะพับ โต๊ะไข่เจียว โต๊ะตั้งแคมป์ ซื้อ 1 แถม 1 ถุงจัดส่ง ง่ายต่อการพกพา ทำความสะอาดง่าย</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/5fnhB6BArU</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>MAX FIRE แก๊สกระป๋อง แก๊สปิคนิค พร้อมด้วยระบบป้องกันการระเบิด ปริมาณ 250g. ประเทศเกาหลี 1 แพ็ค</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/6Ajxm1pku2</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>เชือกพาราคอร์ด เชือกตากผ้า เชือก ยาว4/10เมตร เก็บง่าย คุณภาพดี ทนทาน คละสี สำหรับเดินป่า ตั้งแคมป์ ใช้ผูกเอนกประสงค์</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/AKZWjhSCbh</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>หมอนเป่าลม หมอนหนุนเป่าลมพกพา เบามาก จัดเก็บง่าย ขนาดพกพา 43x28x12cm หมอนเป่าลม ใบใหญ่ เหมาะสำหรับสำนักงาน การท่องเที่ยว</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/4qEaBblIDQ</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>ผ้าบัฟ ผ้าโพกหน้า ทั้งวิ่ง ล่าสัตว์ ตกปลา เดินป่า รถจักรยานยนต์ ปั่นจักรยาน เล่นสกี ชิคสุดๆค่าได้ยาวนานคุ้มค่า</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>https://s.shopee.co.th/3LPmOrdT84</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/review_products.xlsx
+++ b/review_products.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posted_state" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$G$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -790,12 +790,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>เก้าอี้แคมป์ปิ้ง พนักพิงสูง เก้าอี้สนาม พับได้ แบบพกพา ปิคนิค แถมถุงเก็บ รับน้ำหนัก 300KG</t>
+          <t>Mobi GARDEN Camping Tarp Flysheet Shelter Sun Shade Anti-UV Canopy กันน้ําปิกนิกกลางแจ้งราคาพิเศษ!</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AAG6XCsmzJ</t>
+          <t>https://s.shopee.co.th/8AV3flbllA</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>WTHB เก้าอี้แคมป์ปิ้ง เพิ่มผ้าฝ้าย พนักพิงสูง เก้าอี้สนาม เก้าอี้สนามพับได้ ปิคนิค รับน้ำหนัก 300KG</t>
+          <t>Acebeam TAC 2AA SFT 25R Hi ไฟฉาย LED 1600 ลูเมน 181 เมตรไฟฉาย EDC แบบพกพา USB-C แบตเตอรี่ชาร์จปุ่มคู่ flashligt</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4fv9z7LZZT</t>
+          <t>https://s.shopee.co.th/4fvBR9C2Q3</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -828,12 +828,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ซื้อ 1 แถม1ไฟฉายคาดหัว ไฟคาดหัว ส่องไกล ไฟคาดหัว LED ส่องกบ เดินป่า ลุยฝนได้ สว่างมาก รับประกันความสว่า</t>
+          <t>Swiss TECH-16 in 1 Camping Multitool EDC Multi-Folding Plier Wire Stripper กระเป๋ากลางแจ้งมินิแบบพกพาสําหรับ Camping มาใหม่ล่าสุด</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1Vy8DJSgdv</t>
+          <t>https://s.shopee.co.th/3g2eFG36K8</t>
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -847,12 +847,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>20warehouse ไฟฉายคาดศีรษะ LED 90 Lumens ปรับมุมได้ ไฟส่องสว่างพกพา สำหรับเดินป่า กรีดยาง ซ่อมรถ ตกปลา</t>
+          <t>Wurkkos TD11 3000lm สมาร์ท OLED ไฟฉายยุทธวิธี, LED RGB ไฟด้านข้างที่มีสีสัน 320-เมตร, สวิตช์คู่, 3.7V 1670mAh แบตเตอรี่ลิเธียม EDC ไฟฉาย</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/40fTBvEz6Q</t>
+          <t>https://s.shopee.co.th/5fnid02X7w</t>
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -866,12 +866,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ซื้อ1แถม1ไฟฉายแรงสูง ไฟฉายLED ไฟฉายพกพา ชาร์จUSB ส่องสว่างไกล ปรับได้5ระดับ</t>
+          <t>SWISS TECH/16 in 1 Camping Multitool, คีมอเนกประสงค์, EDC Wire Stripper, กระเป๋ากลางแจ้ง, มินิแบบพกพาสําหรับ Camping, มาใหม่ล่าสุด</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/9fJpwLobn1</t>
+          <t>https://s.shopee.co.th/9V0RBxUr5L</t>
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
@@ -885,12 +885,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>530 Portable Flashlights Miniไฟฉายสว่างมาก CREE LED XPE+COB 2in1 600mah usb charge 3mode ซูมได้</t>
+          <t>MOSSY OAK คีมอเนกประสงค์ 19-in-1 สแตนเลสสตีลเครื่องมือ EDC พร้อมไขควงแขน Self-locking พร้อม Sheath-Perfect สําหรับการตั้งแคมป์กลางแจ้งพร้อมกระเป๋า</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2qTVno4nfp</t>
+          <t>https://s.shopee.co.th/2Vqgr5KnGD</t>
         </is>
       </c>
       <c r="D23" s="2" t="n"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>เชือกรอกปรับระดับได้ เชือกเต็นท์ เชือกรอกปรับระดับได้ 4m สําหรับตั้งแคมป์กลางแจ้ง รอกเชือก เชือกยก</t>
+          <t>Sofirn SK1 ไฟฉายยุทธวิธี, 1300 Lumens, กันน้ํา IP68, โยนยาว, ชาร์จใหม่ได้, EDC</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/1qaybz40f6</t>
+          <t>https://s.shopee.co.th/40fUdy84Q9</t>
         </is>
       </c>
       <c r="D24" s="2" t="n"/>
@@ -923,12 +923,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>สมอบกเหล็กหล่อ สมอบกเต็นท์ วงแหวนเรืองแสง 20/30/40 CM เหล็กคาร์บอนสูง</t>
+          <t>NEXTORCH NP12 Ti EDC ปากกาลูกปัดเซรามิคแก้ว Breaker หัวไทเทเนียมปากกาการอยู่รอดฉุกเฉิน Self-defense</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fnhB2pljE</t>
+          <t>https://s.shopee.co.th/7fYn0i2Qis</t>
         </is>
       </c>
       <c r="D25" s="2" t="n"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>มีดตั้งแคมป์กลางแจ้ง (สแตนเลส) - มีดอเนกประสงค์แบบพกพา คมชัดเป็นพิเศษ G3204</t>
+          <t>จัดส่งจากกรุงเทพVOTAGOO กระเป๋าเอวทัคติคอล EDC พกพา ผ้าไนลอน420D ทนทาน ซิปYKK แขนงค์Duraflex กระเป๋าใส่อุปกรณ์กลางแจ้ง ความจุ7ลิตร PISTOL WAIST PACKCOD)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/50Y0Npil9c</t>
+          <t>https://s.shopee.co.th/50Y1poTySo</t>
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>#019 Kershaw #Folding knife #มีดพับ #มีดเดินป่า #มีดเอนกประสงค์ LIFEPLAZA</t>
+          <t>กระเป๋าสะพายข้าง edc compact shoulder helikon codura</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/2gA5bYimaj</t>
+          <t>https://s.shopee.co.th/50Y1psApQp</t>
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NANMEEBOOKS หนังสือ แผนที่ประวัติศาสตร์ เหตุการณ์เปลี่ยนโลก เสริมความรู้</t>
+          <t>Naturehike lw180 ถุงนอนผ้าฝ้าย น้ําหนักเบา สําหรับตั้งแคมป์ เดินป่า กลางแจ้ง แผ่นรองนอน</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6Ajxm0MsFI</t>
+          <t>https://s.shopee.co.th/2qTXGB3YXk</t>
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
@@ -999,12 +999,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>WAYFARER โต๊ะแคมป์กลางแจ้ง โต๊ะพับ โต๊ะไข่เจียว โต๊ะตั้งแคมป์ ซื้อ 1 แถม 1 ถุงจัดส่ง ง่ายต่อการพกพา ทำความสะอาดง่าย</t>
+          <t>เข็มขัด Rattler EDC Belt เข็มขัดแบบใส่ได้ทุกวันสไตล์แทคติคอล</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/5fnhB6BArU</t>
+          <t>https://s.shopee.co.th/AKZYBgqbOA</t>
         </is>
       </c>
       <c r="D29" s="2" t="n"/>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MAX FIRE แก๊สกระป๋อง แก๊สปิคนิค พร้อมด้วยระบบป้องกันการระเบิด ปริมาณ 250g. ประเทศเกาหลี 1 แพ็ค</t>
+          <t>เข็มขัดไนลอน EDC ทรงแข็ง GUNBANGKOK | หัวล็อคออโต้ แข็งแรง ปรับได้ Free Size</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/6Ajxm1pku2</t>
+          <t>https://s.shopee.co.th/2Vqgr7kJbX</t>
         </is>
       </c>
       <c r="D30" s="2" t="n"/>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>เชือกพาราคอร์ด เชือกตากผ้า เชือก ยาว4/10เมตร เก็บง่าย คุณภาพดี ทนทาน คละสี สำหรับเดินป่า ตั้งแคมป์ ใช้ผูกเอนกประสงค์</t>
+          <t>MODOFO ที่นอนลม มีหมอน ที่นอนลมกลางแจ้ง เบาะนอนพกพา 190*60ซม เตียงเป่าลม ที่แคมป์ปิ้ง พกพาสะดวก</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/AKZWjhSCbh</t>
+          <t>https://s.shopee.co.th/7AcWQ5s3Jr</t>
         </is>
       </c>
       <c r="D31" s="2" t="n"/>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>หมอนเป่าลม หมอนหนุนเป่าลมพกพา เบามาก จัดเก็บง่าย ขนาดพกพา 43x28x12cm หมอนเป่าลม ใบใหญ่ เหมาะสำหรับสำนักงาน การท่องเที่ยว</t>
+          <t>WOLF EDC รอกตกปลา เฟืองทองเหลือง 6BB ระบบ Digital Control คลิ๊กเสียงปลาลาก ตกปลา รอกหยดน้ำ รอกเบท</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/4qEaBblIDQ</t>
+          <t>https://s.shopee.co.th/9fJrOK5EOc</t>
         </is>
       </c>
       <c r="D32" s="2" t="n"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ผ้าบัฟ ผ้าโพกหน้า ทั้งวิ่ง ล่าสัตว์ ตกปลา เดินป่า รถจักรยานยนต์ ปั่นจักรยาน เล่นสกี ชิคสุดๆค่าได้ยาวนานคุ้มค่า</t>
+          <t>หนาขึ้น20เท่าPIKA ผ้าเต้นท์ หนา6800D (เฉพาะผ้า)ผ้าใบเต็นท์ กันน้ำ กันแดด กันยูวี 2x2 2x3 3x3 เต็นท์พับได้ เต็นท์ขายของ</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://s.shopee.co.th/3LPmOrdT84</t>
+          <t>https://s.shopee.co.th/5fn14DklSQ</t>
         </is>
       </c>
       <c r="D33" s="2" t="n"/>
@@ -1088,8 +1088,369 @@
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Wurkkos ไฟ EDC WK03 1800lm SST40 USB C ชาร์จซ้ําได้ 18650 UI พร้อมตัวบ่งชี้พลังงาน ATR</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4qEbdNtq5O</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>เก้าอี้แคมป์ปิ้ง คนอ้วน พร้อมกระเป๋าจัดเก็บ โครงอลูมิเนียมรับน้ำหนักได้ 300KG</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9V0RCM6764</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>เปลญวน เก้าอี้ชิงช้า แบบแขวน เก้าอี้นั่งทรงกลม แบบถักแฮนด์เมด สไตล์นอร์ดิก</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7psDDO1ANv</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>PIKA ผ้าเต้นท์ หนาสุดๆ6800D(เฉพาะผ้า)กันน้ำ กันยูวี100% ผ้าใบเต็นท์ เต็นท์ขายของ 2x2 2x3 3x3เมตร ผ้าสวยถูกใจแน่นอน</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3VjE3KKyrA</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>มัลติทูลอเนกประสงค์ TRAVELER ของแท้ 12in1 สีขาว แบบพกพา มีระบบล๊อก EDC แคมป์ปิ้ง ติดรถ งานช่าง มีเลื่อย ไขควง</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/30mxS448y2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Leacat กระเป๋าเป้สะพายหลัง EDC กันน้ํา ขนาด 20 ลิตร สําหรับเดินป่า ล่าสัตว์</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7AcWPiY7uJ</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Free hike เก้าอี้แคมป์ปิ้ง เก้าอี้สนามที่พับได้ camping ขาตั้งอลูมิเนียม รับน้ำหนักได้ 300กก</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Kh103XYhh</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>COD เตาแอลกอฮอล์ เตาแอลกอฮอล์สแตนเลสแบบพกพา เตาตั้งแคมป์สําหรับตั้งแคมป์</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/gP2g8D94P</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ห่วงตัวดี ไทเทเนียม ห่วงเกือกม้า Titanium D-Shackle พร้อมสกรูถอดประกอบ สำหรับพวงกุญแจ EDC มี 2 ขนาด 12mm 17mm</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B6NePzLDc</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>PKT ยางนอกไม่ใช้ยางใน(Tubeless) ขอบ12,13,14,15,10 ZOOMER X,PCX,GRAND FILANO,NMAX พีเคที ยางไทยแท้</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2VqgqGBUTJ</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>MDช่องหลัก นีออนหัวเชื้อสลายคราบช่วงล่าง คราบน้ำมันคราบฝังแน่น คราบฝังตามล้อยาง</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/8V7tzwBGOA</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>ผ้าคลุมรถมอเตอร์ไซค์ กันน้ำ กันฝุ่น กันแดด หนา 5 ชั้น วัสดุทนทาน สีดำ ขนาด M/ L / XL / XXL</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/111t3VPrXd</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>หมวกกันน๊อค motorcycle helmet ส่งจากกทม. COD ได้ เลนส์คู่ กันแดด ระบายอากาศ ABS แข็งแรง</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/7VFMnV46DI</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>FOAMING CLEANER ผลิตภัณฑ์ทำความสะอาดในรถยนต์ เบาะ คอนโซล พรมปูพื้นรถยนต์</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/2LXGeccjdi</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>KATHWI น้ําหอมติดรถยนต์ K-nature, Rose Forest, Yu Long Tea, Eternal Water Balm, กลิ่นหอมติดทนนานและน่ารื่นรมย์, น้ําหอมติดรถยนต์สุดหรูล่าสุด 180g</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/9Kh0zPnAOe</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>ENDURO 4T RACING 10W-40 ขนาด 0.8L น้ำมันเครื่องรถจักรยานยนต์ 4 จังหวะคุณภาพสูง</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/4VblDqEpBe</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Nano Ceramic Window Film ฟิล์มกรองแสงรถยนต์ ฟิล์มกรองแสง ฟิล์มอาคาร เซรามิค (ราคาต่อเมตร)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3B6Ne6CETd</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>TwoStar เสื้อแจ็คเก็ตบอมเบอร์เรียบๆ สำหรับผู้ชายและผู้หญิง คุณภาพสูง เสื้อโค้ททรงมอเตอร์ไซค์ คอกลม ขนาดกำลังดี</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/20uQFIeFPs</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>หัวฉีดเเต่ง 6รู J 125CC 150CC(สั้น) 6รู G 145 150CC 8รูJ W 170CC(สั้น) ใส่กับ click125i wave110i new KZR คลิก125ไอ KYZ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://s.shopee.co.th/3LPnplDFaz</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G33"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
